--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8033" uniqueCount="1385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8424" uniqueCount="1403">
   <si>
     <t>leave_id</t>
   </si>
@@ -4166,6 +4166,60 @@
   </si>
   <si>
     <t>LV-837</t>
+  </si>
+  <si>
+    <t>فيصل سعد عبدالله الشمري</t>
+  </si>
+  <si>
+    <t>FAISAL SAAD ALSHAMMARI</t>
+  </si>
+  <si>
+    <t>Industrial Engineer - مهندس صناعي</t>
+  </si>
+  <si>
+    <t>NAWAF NAWAR ALOTAIBI</t>
+  </si>
+  <si>
+    <t>هتان سليمان الغازي</t>
+  </si>
+  <si>
+    <t>HATTAN SULAIMAN ALGHZEE</t>
+  </si>
+  <si>
+    <t>GN | Procurement</t>
+  </si>
+  <si>
+    <t>راشد فائز سويحل الشمري</t>
+  </si>
+  <si>
+    <t>محمد ريان خالد</t>
+  </si>
+  <si>
+    <t>MD RAIYAN KHALID</t>
+  </si>
+  <si>
+    <t>هوم بهادور كومال</t>
+  </si>
+  <si>
+    <t>HUM BAHADUR KUMAL</t>
+  </si>
+  <si>
+    <t>دابلو كومار</t>
+  </si>
+  <si>
+    <t>DABLU KUMAR</t>
+  </si>
+  <si>
+    <t>نانو بينوا</t>
+  </si>
+  <si>
+    <t>NANU THANKAPPAN BINU</t>
+  </si>
+  <si>
+    <t>جوهر الاسلام كالو مياه</t>
+  </si>
+  <si>
+    <t>JOHIRUL ISLAM KALU MIAH</t>
   </si>
 </sst>
 </file>
@@ -4176,7 +4230,7 @@
     <numFmt numFmtId="164" formatCode="yyyy/MM/dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -4208,6 +4262,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="5">
@@ -4242,7 +4300,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -4303,11 +4361,14 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="1" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -40076,24 +40137,14 @@
       <c r="A805" s="6" t="s">
         <v>1350</v>
       </c>
-      <c r="B805" s="8">
-        <v>30497.0</v>
-      </c>
-      <c r="C805" s="14">
-        <v>30497.0</v>
-      </c>
+      <c r="B805" s="17"/>
+      <c r="C805" s="14"/>
       <c r="D805" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E805" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="F805" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="G805" s="16" t="s">
-        <v>1209</v>
-      </c>
+      <c r="E805" s="15"/>
+      <c r="F805" s="15"/>
+      <c r="G805" s="15"/>
       <c r="H805" s="10" t="s">
         <v>19</v>
       </c>
@@ -40120,24 +40171,14 @@
       <c r="A806" s="6" t="s">
         <v>1351</v>
       </c>
-      <c r="B806" s="8">
-        <v>30497.0</v>
-      </c>
-      <c r="C806" s="14">
-        <v>30497.0</v>
-      </c>
+      <c r="B806" s="17"/>
+      <c r="C806" s="14"/>
       <c r="D806" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E806" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="F806" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="G806" s="16" t="s">
-        <v>1209</v>
-      </c>
+      <c r="E806" s="15"/>
+      <c r="F806" s="15"/>
+      <c r="G806" s="15"/>
       <c r="H806" s="10" t="s">
         <v>19</v>
       </c>
@@ -40164,24 +40205,14 @@
       <c r="A807" s="6" t="s">
         <v>1352</v>
       </c>
-      <c r="B807" s="8">
-        <v>30497.0</v>
-      </c>
-      <c r="C807" s="14">
-        <v>30497.0</v>
-      </c>
+      <c r="B807" s="17"/>
+      <c r="C807" s="14"/>
       <c r="D807" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E807" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="F807" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="G807" s="16" t="s">
-        <v>1209</v>
-      </c>
+      <c r="E807" s="15"/>
+      <c r="F807" s="15"/>
+      <c r="G807" s="15"/>
       <c r="H807" s="10" t="s">
         <v>19</v>
       </c>
@@ -41262,17 +41293,33 @@
     </row>
     <row r="832" ht="18.0" customHeight="1">
       <c r="A832" s="6"/>
-      <c r="B832" s="17"/>
-      <c r="C832" s="14"/>
-      <c r="D832" s="20"/>
-      <c r="E832" s="15"/>
-      <c r="F832" s="15"/>
-      <c r="G832" s="15"/>
+      <c r="B832" s="8">
+        <v>27943.0</v>
+      </c>
+      <c r="C832" s="14">
+        <v>27943.0</v>
+      </c>
+      <c r="D832" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E832" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="F832" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="G832" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H832" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I832" s="21"/>
-      <c r="J832" s="21"/>
+      <c r="I832" s="11">
+        <v>46291.0</v>
+      </c>
+      <c r="J832" s="11">
+        <v>46291.0</v>
+      </c>
       <c r="K832" s="10" t="s">
         <v>20</v>
       </c>
@@ -41288,17 +41335,33 @@
     </row>
     <row r="833" ht="18.0" customHeight="1">
       <c r="A833" s="6"/>
-      <c r="B833" s="17"/>
-      <c r="C833" s="14"/>
-      <c r="D833" s="20"/>
-      <c r="E833" s="15"/>
-      <c r="F833" s="15"/>
-      <c r="G833" s="15"/>
+      <c r="B833" s="8">
+        <v>27943.0</v>
+      </c>
+      <c r="C833" s="14">
+        <v>27943.0</v>
+      </c>
+      <c r="D833" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E833" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="F833" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="G833" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H833" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I833" s="21"/>
-      <c r="J833" s="21"/>
+      <c r="I833" s="11">
+        <v>46275.0</v>
+      </c>
+      <c r="J833" s="11">
+        <v>46275.0</v>
+      </c>
       <c r="K833" s="10" t="s">
         <v>20</v>
       </c>
@@ -41314,17 +41377,33 @@
     </row>
     <row r="834" ht="18.0" customHeight="1">
       <c r="A834" s="6"/>
-      <c r="B834" s="17"/>
-      <c r="C834" s="14"/>
-      <c r="D834" s="20"/>
-      <c r="E834" s="15"/>
-      <c r="F834" s="15"/>
-      <c r="G834" s="15"/>
+      <c r="B834" s="8">
+        <v>27509.0</v>
+      </c>
+      <c r="C834" s="14">
+        <v>27509.0</v>
+      </c>
+      <c r="D834" s="9" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E834" s="16" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F834" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="G834" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H834" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I834" s="21"/>
-      <c r="J834" s="21"/>
+      <c r="I834" s="11">
+        <v>46280.0</v>
+      </c>
+      <c r="J834" s="11">
+        <v>46280.0</v>
+      </c>
       <c r="K834" s="10" t="s">
         <v>20</v>
       </c>
@@ -41340,17 +41419,33 @@
     </row>
     <row r="835" ht="18.0" customHeight="1">
       <c r="A835" s="6"/>
-      <c r="B835" s="17"/>
-      <c r="C835" s="14"/>
-      <c r="D835" s="20"/>
-      <c r="E835" s="15"/>
-      <c r="F835" s="15"/>
-      <c r="G835" s="15"/>
+      <c r="B835" s="8">
+        <v>27509.0</v>
+      </c>
+      <c r="C835" s="14">
+        <v>27509.0</v>
+      </c>
+      <c r="D835" s="9" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E835" s="16" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F835" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="G835" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H835" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I835" s="21"/>
-      <c r="J835" s="21"/>
+      <c r="I835" s="11">
+        <v>46277.0</v>
+      </c>
+      <c r="J835" s="11">
+        <v>46277.0</v>
+      </c>
       <c r="K835" s="10" t="s">
         <v>20</v>
       </c>
@@ -41366,17 +41461,33 @@
     </row>
     <row r="836" ht="18.0" customHeight="1">
       <c r="A836" s="6"/>
-      <c r="B836" s="17"/>
-      <c r="C836" s="14"/>
-      <c r="D836" s="20"/>
-      <c r="E836" s="15"/>
-      <c r="F836" s="15"/>
-      <c r="G836" s="15"/>
+      <c r="B836" s="8">
+        <v>32083.0</v>
+      </c>
+      <c r="C836" s="14">
+        <v>32083.0</v>
+      </c>
+      <c r="D836" s="9" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E836" s="16" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F836" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G836" s="18" t="s">
+        <v>1294</v>
+      </c>
       <c r="H836" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I836" s="21"/>
-      <c r="J836" s="21"/>
+      <c r="I836" s="11">
+        <v>46274.0</v>
+      </c>
+      <c r="J836" s="11">
+        <v>46274.0</v>
+      </c>
       <c r="K836" s="10" t="s">
         <v>20</v>
       </c>
@@ -41392,17 +41503,33 @@
     </row>
     <row r="837" ht="18.0" customHeight="1">
       <c r="A837" s="6"/>
-      <c r="B837" s="17"/>
-      <c r="C837" s="14"/>
-      <c r="D837" s="20"/>
-      <c r="E837" s="15"/>
-      <c r="F837" s="15"/>
-      <c r="G837" s="15"/>
+      <c r="B837" s="8">
+        <v>30576.0</v>
+      </c>
+      <c r="C837" s="14">
+        <v>30576.0</v>
+      </c>
+      <c r="D837" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="E837" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="F837" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G837" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H837" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I837" s="21"/>
-      <c r="J837" s="21"/>
+      <c r="I837" s="11">
+        <v>46300.0</v>
+      </c>
+      <c r="J837" s="11">
+        <v>46300.0</v>
+      </c>
       <c r="K837" s="10" t="s">
         <v>20</v>
       </c>
@@ -41418,17 +41545,33 @@
     </row>
     <row r="838" ht="18.0" customHeight="1">
       <c r="A838" s="6"/>
-      <c r="B838" s="17"/>
-      <c r="C838" s="14"/>
-      <c r="D838" s="20"/>
-      <c r="E838" s="15"/>
-      <c r="F838" s="15"/>
-      <c r="G838" s="15"/>
+      <c r="B838" s="8">
+        <v>30560.0</v>
+      </c>
+      <c r="C838" s="14">
+        <v>30560.0</v>
+      </c>
+      <c r="D838" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E838" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="F838" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G838" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H838" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I838" s="21"/>
-      <c r="J838" s="21"/>
+      <c r="I838" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J838" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K838" s="10" t="s">
         <v>20</v>
       </c>
@@ -41444,17 +41587,33 @@
     </row>
     <row r="839" ht="18.0" customHeight="1">
       <c r="A839" s="6"/>
-      <c r="B839" s="17"/>
-      <c r="C839" s="14"/>
-      <c r="D839" s="20"/>
-      <c r="E839" s="15"/>
-      <c r="F839" s="15"/>
-      <c r="G839" s="15"/>
+      <c r="B839" s="8">
+        <v>30560.0</v>
+      </c>
+      <c r="C839" s="14">
+        <v>30560.0</v>
+      </c>
+      <c r="D839" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E839" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="F839" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G839" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H839" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I839" s="21"/>
-      <c r="J839" s="21"/>
+      <c r="I839" s="11">
+        <v>46280.0</v>
+      </c>
+      <c r="J839" s="11">
+        <v>46280.0</v>
+      </c>
       <c r="K839" s="10" t="s">
         <v>20</v>
       </c>
@@ -41470,17 +41629,33 @@
     </row>
     <row r="840" ht="18.0" customHeight="1">
       <c r="A840" s="6"/>
-      <c r="B840" s="17"/>
-      <c r="C840" s="14"/>
-      <c r="D840" s="20"/>
-      <c r="E840" s="15"/>
-      <c r="F840" s="15"/>
-      <c r="G840" s="15"/>
+      <c r="B840" s="8">
+        <v>30560.0</v>
+      </c>
+      <c r="C840" s="14">
+        <v>30560.0</v>
+      </c>
+      <c r="D840" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E840" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="F840" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G840" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H840" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I840" s="21"/>
-      <c r="J840" s="21"/>
+      <c r="I840" s="11">
+        <v>46278.0</v>
+      </c>
+      <c r="J840" s="11">
+        <v>46278.0</v>
+      </c>
       <c r="K840" s="10" t="s">
         <v>20</v>
       </c>
@@ -41496,17 +41671,33 @@
     </row>
     <row r="841" ht="18.0" customHeight="1">
       <c r="A841" s="6"/>
-      <c r="B841" s="17"/>
-      <c r="C841" s="14"/>
-      <c r="D841" s="20"/>
-      <c r="E841" s="15"/>
-      <c r="F841" s="15"/>
-      <c r="G841" s="15"/>
+      <c r="B841" s="8">
+        <v>30536.0</v>
+      </c>
+      <c r="C841" s="14">
+        <v>30536.0</v>
+      </c>
+      <c r="D841" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E841" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F841" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G841" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H841" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I841" s="21"/>
-      <c r="J841" s="21"/>
+      <c r="I841" s="11">
+        <v>46287.0</v>
+      </c>
+      <c r="J841" s="11">
+        <v>46287.0</v>
+      </c>
       <c r="K841" s="10" t="s">
         <v>20</v>
       </c>
@@ -41522,17 +41713,33 @@
     </row>
     <row r="842" ht="18.0" customHeight="1">
       <c r="A842" s="6"/>
-      <c r="B842" s="17"/>
-      <c r="C842" s="14"/>
-      <c r="D842" s="20"/>
-      <c r="E842" s="15"/>
-      <c r="F842" s="15"/>
-      <c r="G842" s="15"/>
+      <c r="B842" s="8">
+        <v>30536.0</v>
+      </c>
+      <c r="C842" s="14">
+        <v>30536.0</v>
+      </c>
+      <c r="D842" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E842" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F842" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G842" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H842" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I842" s="21"/>
-      <c r="J842" s="21"/>
+      <c r="I842" s="11">
+        <v>46292.0</v>
+      </c>
+      <c r="J842" s="11">
+        <v>46292.0</v>
+      </c>
       <c r="K842" s="10" t="s">
         <v>20</v>
       </c>
@@ -41548,17 +41755,33 @@
     </row>
     <row r="843" ht="18.0" customHeight="1">
       <c r="A843" s="6"/>
-      <c r="B843" s="17"/>
-      <c r="C843" s="14"/>
-      <c r="D843" s="20"/>
-      <c r="E843" s="15"/>
-      <c r="F843" s="15"/>
-      <c r="G843" s="15"/>
+      <c r="B843" s="8">
+        <v>29446.0</v>
+      </c>
+      <c r="C843" s="14">
+        <v>29446.0</v>
+      </c>
+      <c r="D843" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E843" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F843" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G843" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H843" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I843" s="21"/>
-      <c r="J843" s="21"/>
+      <c r="I843" s="11">
+        <v>46298.0</v>
+      </c>
+      <c r="J843" s="11">
+        <v>46298.0</v>
+      </c>
       <c r="K843" s="10" t="s">
         <v>20</v>
       </c>
@@ -41574,17 +41797,33 @@
     </row>
     <row r="844" ht="18.0" customHeight="1">
       <c r="A844" s="6"/>
-      <c r="B844" s="17"/>
-      <c r="C844" s="14"/>
-      <c r="D844" s="20"/>
-      <c r="E844" s="15"/>
-      <c r="F844" s="15"/>
-      <c r="G844" s="15"/>
+      <c r="B844" s="8">
+        <v>29446.0</v>
+      </c>
+      <c r="C844" s="14">
+        <v>29446.0</v>
+      </c>
+      <c r="D844" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E844" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F844" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G844" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H844" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I844" s="21"/>
-      <c r="J844" s="21"/>
+      <c r="I844" s="11">
+        <v>46293.0</v>
+      </c>
+      <c r="J844" s="11">
+        <v>46293.0</v>
+      </c>
       <c r="K844" s="10" t="s">
         <v>20</v>
       </c>
@@ -41600,17 +41839,33 @@
     </row>
     <row r="845" ht="18.0" customHeight="1">
       <c r="A845" s="6"/>
-      <c r="B845" s="17"/>
-      <c r="C845" s="14"/>
-      <c r="D845" s="20"/>
-      <c r="E845" s="15"/>
-      <c r="F845" s="15"/>
-      <c r="G845" s="15"/>
+      <c r="B845" s="8">
+        <v>29446.0</v>
+      </c>
+      <c r="C845" s="14">
+        <v>29446.0</v>
+      </c>
+      <c r="D845" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E845" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F845" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G845" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H845" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I845" s="21"/>
-      <c r="J845" s="21"/>
+      <c r="I845" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J845" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K845" s="10" t="s">
         <v>20</v>
       </c>
@@ -41626,17 +41881,33 @@
     </row>
     <row r="846" ht="18.0" customHeight="1">
       <c r="A846" s="6"/>
-      <c r="B846" s="17"/>
-      <c r="C846" s="14"/>
-      <c r="D846" s="20"/>
-      <c r="E846" s="15"/>
-      <c r="F846" s="15"/>
-      <c r="G846" s="15"/>
+      <c r="B846" s="8">
+        <v>29446.0</v>
+      </c>
+      <c r="C846" s="14">
+        <v>29446.0</v>
+      </c>
+      <c r="D846" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E846" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F846" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G846" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H846" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I846" s="21"/>
-      <c r="J846" s="21"/>
+      <c r="I846" s="11">
+        <v>46285.0</v>
+      </c>
+      <c r="J846" s="11">
+        <v>46285.0</v>
+      </c>
       <c r="K846" s="10" t="s">
         <v>20</v>
       </c>
@@ -41652,17 +41923,33 @@
     </row>
     <row r="847" ht="18.0" customHeight="1">
       <c r="A847" s="6"/>
-      <c r="B847" s="17"/>
-      <c r="C847" s="14"/>
-      <c r="D847" s="20"/>
-      <c r="E847" s="15"/>
-      <c r="F847" s="15"/>
-      <c r="G847" s="15"/>
+      <c r="B847" s="8">
+        <v>29446.0</v>
+      </c>
+      <c r="C847" s="14">
+        <v>29446.0</v>
+      </c>
+      <c r="D847" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E847" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F847" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G847" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H847" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I847" s="21"/>
-      <c r="J847" s="21"/>
+      <c r="I847" s="11">
+        <v>46277.0</v>
+      </c>
+      <c r="J847" s="11">
+        <v>46277.0</v>
+      </c>
       <c r="K847" s="10" t="s">
         <v>20</v>
       </c>
@@ -41678,17 +41965,33 @@
     </row>
     <row r="848" ht="18.0" customHeight="1">
       <c r="A848" s="6"/>
-      <c r="B848" s="17"/>
-      <c r="C848" s="14"/>
-      <c r="D848" s="20"/>
-      <c r="E848" s="15"/>
-      <c r="F848" s="15"/>
-      <c r="G848" s="15"/>
+      <c r="B848" s="8">
+        <v>29446.0</v>
+      </c>
+      <c r="C848" s="14">
+        <v>29446.0</v>
+      </c>
+      <c r="D848" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E848" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F848" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G848" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H848" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I848" s="21"/>
-      <c r="J848" s="21"/>
+      <c r="I848" s="11">
+        <v>46278.0</v>
+      </c>
+      <c r="J848" s="11">
+        <v>46278.0</v>
+      </c>
       <c r="K848" s="10" t="s">
         <v>20</v>
       </c>
@@ -41704,17 +42007,33 @@
     </row>
     <row r="849" ht="18.0" customHeight="1">
       <c r="A849" s="6"/>
-      <c r="B849" s="17"/>
-      <c r="C849" s="14"/>
-      <c r="D849" s="20"/>
-      <c r="E849" s="15"/>
-      <c r="F849" s="15"/>
-      <c r="G849" s="15"/>
+      <c r="B849" s="8">
+        <v>29442.0</v>
+      </c>
+      <c r="C849" s="14">
+        <v>29442.0</v>
+      </c>
+      <c r="D849" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="E849" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="F849" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G849" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H849" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I849" s="21"/>
-      <c r="J849" s="21"/>
+      <c r="I849" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J849" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K849" s="10" t="s">
         <v>20</v>
       </c>
@@ -41730,17 +42049,33 @@
     </row>
     <row r="850" ht="18.0" customHeight="1">
       <c r="A850" s="6"/>
-      <c r="B850" s="17"/>
-      <c r="C850" s="14"/>
-      <c r="D850" s="20"/>
-      <c r="E850" s="15"/>
-      <c r="F850" s="15"/>
-      <c r="G850" s="15"/>
+      <c r="B850" s="8">
+        <v>31731.0</v>
+      </c>
+      <c r="C850" s="14">
+        <v>31731.0</v>
+      </c>
+      <c r="D850" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E850" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="F850" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G850" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H850" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I850" s="21"/>
-      <c r="J850" s="21"/>
+      <c r="I850" s="11">
+        <v>46284.0</v>
+      </c>
+      <c r="J850" s="11">
+        <v>46284.0</v>
+      </c>
       <c r="K850" s="10" t="s">
         <v>20</v>
       </c>
@@ -41756,17 +42091,33 @@
     </row>
     <row r="851" ht="18.0" customHeight="1">
       <c r="A851" s="6"/>
-      <c r="B851" s="17"/>
-      <c r="C851" s="14"/>
-      <c r="D851" s="20"/>
-      <c r="E851" s="15"/>
-      <c r="F851" s="15"/>
-      <c r="G851" s="15"/>
+      <c r="B851" s="8">
+        <v>31731.0</v>
+      </c>
+      <c r="C851" s="14">
+        <v>31731.0</v>
+      </c>
+      <c r="D851" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E851" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="F851" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G851" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H851" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I851" s="21"/>
-      <c r="J851" s="21"/>
+      <c r="I851" s="11">
+        <v>46291.0</v>
+      </c>
+      <c r="J851" s="11">
+        <v>46291.0</v>
+      </c>
       <c r="K851" s="10" t="s">
         <v>20</v>
       </c>
@@ -41782,17 +42133,33 @@
     </row>
     <row r="852" ht="18.0" customHeight="1">
       <c r="A852" s="6"/>
-      <c r="B852" s="17"/>
-      <c r="C852" s="14"/>
-      <c r="D852" s="20"/>
-      <c r="E852" s="15"/>
-      <c r="F852" s="15"/>
-      <c r="G852" s="15"/>
+      <c r="B852" s="8">
+        <v>31731.0</v>
+      </c>
+      <c r="C852" s="14">
+        <v>31731.0</v>
+      </c>
+      <c r="D852" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E852" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="F852" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G852" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H852" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I852" s="21"/>
-      <c r="J852" s="21"/>
+      <c r="I852" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J852" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K852" s="10" t="s">
         <v>20</v>
       </c>
@@ -41808,17 +42175,33 @@
     </row>
     <row r="853" ht="18.0" customHeight="1">
       <c r="A853" s="6"/>
-      <c r="B853" s="17"/>
-      <c r="C853" s="14"/>
-      <c r="D853" s="20"/>
-      <c r="E853" s="15"/>
-      <c r="F853" s="15"/>
-      <c r="G853" s="15"/>
+      <c r="B853" s="8">
+        <v>31731.0</v>
+      </c>
+      <c r="C853" s="14">
+        <v>31731.0</v>
+      </c>
+      <c r="D853" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E853" s="16" t="s">
+        <v>638</v>
+      </c>
+      <c r="F853" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G853" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H853" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I853" s="21"/>
-      <c r="J853" s="21"/>
+      <c r="I853" s="11">
+        <v>46285.0</v>
+      </c>
+      <c r="J853" s="11">
+        <v>46285.0</v>
+      </c>
       <c r="K853" s="10" t="s">
         <v>20</v>
       </c>
@@ -41834,17 +42217,33 @@
     </row>
     <row r="854" ht="18.0" customHeight="1">
       <c r="A854" s="6"/>
-      <c r="B854" s="17"/>
-      <c r="C854" s="14"/>
-      <c r="D854" s="20"/>
-      <c r="E854" s="15"/>
-      <c r="F854" s="15"/>
-      <c r="G854" s="15"/>
+      <c r="B854" s="8">
+        <v>32877.0</v>
+      </c>
+      <c r="C854" s="14">
+        <v>32877.0</v>
+      </c>
+      <c r="D854" s="9" t="s">
+        <v>970</v>
+      </c>
+      <c r="E854" s="16" t="s">
+        <v>971</v>
+      </c>
+      <c r="F854" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G854" s="18" t="s">
+        <v>1387</v>
+      </c>
       <c r="H854" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I854" s="21"/>
-      <c r="J854" s="21"/>
+      <c r="I854" s="11">
+        <v>46291.0</v>
+      </c>
+      <c r="J854" s="11">
+        <v>46291.0</v>
+      </c>
       <c r="K854" s="10" t="s">
         <v>20</v>
       </c>
@@ -41860,17 +42259,33 @@
     </row>
     <row r="855" ht="18.0" customHeight="1">
       <c r="A855" s="6"/>
-      <c r="B855" s="17"/>
-      <c r="C855" s="14"/>
-      <c r="D855" s="20"/>
-      <c r="E855" s="15"/>
-      <c r="F855" s="15"/>
-      <c r="G855" s="15"/>
+      <c r="B855" s="8">
+        <v>31354.0</v>
+      </c>
+      <c r="C855" s="14">
+        <v>31354.0</v>
+      </c>
+      <c r="D855" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E855" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="F855" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G855" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H855" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I855" s="21"/>
-      <c r="J855" s="21"/>
+      <c r="I855" s="11">
+        <v>46299.0</v>
+      </c>
+      <c r="J855" s="11">
+        <v>46302.0</v>
+      </c>
       <c r="K855" s="10" t="s">
         <v>20</v>
       </c>
@@ -41886,17 +42301,33 @@
     </row>
     <row r="856" ht="18.0" customHeight="1">
       <c r="A856" s="6"/>
-      <c r="B856" s="17"/>
-      <c r="C856" s="14"/>
-      <c r="D856" s="20"/>
-      <c r="E856" s="15"/>
-      <c r="F856" s="15"/>
-      <c r="G856" s="15"/>
+      <c r="B856" s="8">
+        <v>29977.0</v>
+      </c>
+      <c r="C856" s="14">
+        <v>29977.0</v>
+      </c>
+      <c r="D856" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E856" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="F856" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G856" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H856" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I856" s="21"/>
-      <c r="J856" s="21"/>
+      <c r="I856" s="11">
+        <v>46298.0</v>
+      </c>
+      <c r="J856" s="11">
+        <v>46298.0</v>
+      </c>
       <c r="K856" s="10" t="s">
         <v>20</v>
       </c>
@@ -41912,17 +42343,33 @@
     </row>
     <row r="857" ht="18.0" customHeight="1">
       <c r="A857" s="6"/>
-      <c r="B857" s="17"/>
-      <c r="C857" s="14"/>
-      <c r="D857" s="20"/>
-      <c r="E857" s="15"/>
-      <c r="F857" s="15"/>
-      <c r="G857" s="15"/>
+      <c r="B857" s="8">
+        <v>32877.0</v>
+      </c>
+      <c r="C857" s="14">
+        <v>32877.0</v>
+      </c>
+      <c r="D857" s="9" t="s">
+        <v>970</v>
+      </c>
+      <c r="E857" s="16" t="s">
+        <v>971</v>
+      </c>
+      <c r="F857" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G857" s="18" t="s">
+        <v>1387</v>
+      </c>
       <c r="H857" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I857" s="21"/>
-      <c r="J857" s="21"/>
+      <c r="I857" s="11">
+        <v>46273.0</v>
+      </c>
+      <c r="J857" s="11">
+        <v>46273.0</v>
+      </c>
       <c r="K857" s="10" t="s">
         <v>20</v>
       </c>
@@ -41938,17 +42385,33 @@
     </row>
     <row r="858" ht="18.0" customHeight="1">
       <c r="A858" s="6"/>
-      <c r="B858" s="17"/>
-      <c r="C858" s="14"/>
-      <c r="D858" s="20"/>
-      <c r="E858" s="15"/>
-      <c r="F858" s="15"/>
-      <c r="G858" s="15"/>
+      <c r="B858" s="8">
+        <v>30584.0</v>
+      </c>
+      <c r="C858" s="14">
+        <v>30584.0</v>
+      </c>
+      <c r="D858" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E858" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="F858" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G858" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H858" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I858" s="21"/>
-      <c r="J858" s="21"/>
+      <c r="I858" s="11">
+        <v>46275.0</v>
+      </c>
+      <c r="J858" s="11">
+        <v>46275.0</v>
+      </c>
       <c r="K858" s="10" t="s">
         <v>20</v>
       </c>
@@ -41964,17 +42427,33 @@
     </row>
     <row r="859" ht="18.0" customHeight="1">
       <c r="A859" s="6"/>
-      <c r="B859" s="17"/>
-      <c r="C859" s="14"/>
-      <c r="D859" s="20"/>
-      <c r="E859" s="15"/>
-      <c r="F859" s="15"/>
-      <c r="G859" s="15"/>
+      <c r="B859" s="8">
+        <v>30584.0</v>
+      </c>
+      <c r="C859" s="14">
+        <v>30584.0</v>
+      </c>
+      <c r="D859" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E859" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="F859" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G859" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H859" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I859" s="21"/>
-      <c r="J859" s="21"/>
+      <c r="I859" s="11">
+        <v>46278.0</v>
+      </c>
+      <c r="J859" s="11">
+        <v>46278.0</v>
+      </c>
       <c r="K859" s="10" t="s">
         <v>20</v>
       </c>
@@ -41990,17 +42469,33 @@
     </row>
     <row r="860" ht="18.0" customHeight="1">
       <c r="A860" s="6"/>
-      <c r="B860" s="17"/>
-      <c r="C860" s="14"/>
-      <c r="D860" s="20"/>
-      <c r="E860" s="15"/>
-      <c r="F860" s="15"/>
-      <c r="G860" s="15"/>
+      <c r="B860" s="8">
+        <v>30584.0</v>
+      </c>
+      <c r="C860" s="14">
+        <v>30584.0</v>
+      </c>
+      <c r="D860" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E860" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="F860" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G860" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H860" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I860" s="21"/>
-      <c r="J860" s="21"/>
+      <c r="I860" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J860" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K860" s="10" t="s">
         <v>20</v>
       </c>
@@ -42016,17 +42511,33 @@
     </row>
     <row r="861" ht="18.0" customHeight="1">
       <c r="A861" s="6"/>
-      <c r="B861" s="17"/>
-      <c r="C861" s="14"/>
-      <c r="D861" s="20"/>
-      <c r="E861" s="15"/>
-      <c r="F861" s="15"/>
-      <c r="G861" s="15"/>
+      <c r="B861" s="8">
+        <v>29862.0</v>
+      </c>
+      <c r="C861" s="14">
+        <v>29862.0</v>
+      </c>
+      <c r="D861" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="E861" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="F861" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G861" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H861" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I861" s="21"/>
-      <c r="J861" s="21"/>
+      <c r="I861" s="11">
+        <v>46286.0</v>
+      </c>
+      <c r="J861" s="11">
+        <v>46286.0</v>
+      </c>
       <c r="K861" s="10" t="s">
         <v>20</v>
       </c>
@@ -42042,17 +42553,33 @@
     </row>
     <row r="862" ht="18.0" customHeight="1">
       <c r="A862" s="6"/>
-      <c r="B862" s="17"/>
-      <c r="C862" s="14"/>
-      <c r="D862" s="20"/>
-      <c r="E862" s="15"/>
-      <c r="F862" s="15"/>
-      <c r="G862" s="15"/>
+      <c r="B862" s="8">
+        <v>29862.0</v>
+      </c>
+      <c r="C862" s="14">
+        <v>29862.0</v>
+      </c>
+      <c r="D862" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="E862" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="F862" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G862" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H862" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I862" s="21"/>
-      <c r="J862" s="21"/>
+      <c r="I862" s="11">
+        <v>46279.0</v>
+      </c>
+      <c r="J862" s="11">
+        <v>46279.0</v>
+      </c>
       <c r="K862" s="10" t="s">
         <v>20</v>
       </c>
@@ -42068,17 +42595,33 @@
     </row>
     <row r="863" ht="18.0" customHeight="1">
       <c r="A863" s="6"/>
-      <c r="B863" s="17"/>
-      <c r="C863" s="14"/>
-      <c r="D863" s="20"/>
-      <c r="E863" s="15"/>
-      <c r="F863" s="15"/>
-      <c r="G863" s="15"/>
+      <c r="B863" s="8">
+        <v>29858.0</v>
+      </c>
+      <c r="C863" s="14">
+        <v>29858.0</v>
+      </c>
+      <c r="D863" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E863" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="F863" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G863" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H863" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I863" s="21"/>
-      <c r="J863" s="21"/>
+      <c r="I863" s="11">
+        <v>46278.0</v>
+      </c>
+      <c r="J863" s="11">
+        <v>46278.0</v>
+      </c>
       <c r="K863" s="10" t="s">
         <v>20</v>
       </c>
@@ -42094,17 +42637,33 @@
     </row>
     <row r="864" ht="18.0" customHeight="1">
       <c r="A864" s="6"/>
-      <c r="B864" s="17"/>
-      <c r="C864" s="14"/>
-      <c r="D864" s="20"/>
-      <c r="E864" s="15"/>
-      <c r="F864" s="15"/>
-      <c r="G864" s="15"/>
+      <c r="B864" s="8">
+        <v>29858.0</v>
+      </c>
+      <c r="C864" s="14">
+        <v>29858.0</v>
+      </c>
+      <c r="D864" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E864" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="F864" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G864" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H864" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I864" s="21"/>
-      <c r="J864" s="21"/>
+      <c r="I864" s="11">
+        <v>46294.0</v>
+      </c>
+      <c r="J864" s="11">
+        <v>46294.0</v>
+      </c>
       <c r="K864" s="10" t="s">
         <v>20</v>
       </c>
@@ -42120,17 +42679,33 @@
     </row>
     <row r="865" ht="18.0" customHeight="1">
       <c r="A865" s="6"/>
-      <c r="B865" s="17"/>
-      <c r="C865" s="14"/>
-      <c r="D865" s="20"/>
-      <c r="E865" s="15"/>
-      <c r="F865" s="15"/>
-      <c r="G865" s="15"/>
+      <c r="B865" s="8">
+        <v>29858.0</v>
+      </c>
+      <c r="C865" s="14">
+        <v>29858.0</v>
+      </c>
+      <c r="D865" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="E865" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="F865" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G865" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H865" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I865" s="21"/>
-      <c r="J865" s="21"/>
+      <c r="I865" s="11">
+        <v>46287.0</v>
+      </c>
+      <c r="J865" s="11">
+        <v>46287.0</v>
+      </c>
       <c r="K865" s="10" t="s">
         <v>20</v>
       </c>
@@ -42146,17 +42721,33 @@
     </row>
     <row r="866" ht="18.0" customHeight="1">
       <c r="A866" s="6"/>
-      <c r="B866" s="17"/>
-      <c r="C866" s="14"/>
-      <c r="D866" s="20"/>
-      <c r="E866" s="15"/>
-      <c r="F866" s="15"/>
-      <c r="G866" s="15"/>
+      <c r="B866" s="8">
+        <v>26390.0</v>
+      </c>
+      <c r="C866" s="14">
+        <v>26390.0</v>
+      </c>
+      <c r="D866" s="9" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E866" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F866" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G866" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H866" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I866" s="21"/>
-      <c r="J866" s="21"/>
+      <c r="I866" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J866" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K866" s="10" t="s">
         <v>20</v>
       </c>
@@ -42172,17 +42763,33 @@
     </row>
     <row r="867" ht="18.0" customHeight="1">
       <c r="A867" s="6"/>
-      <c r="B867" s="17"/>
-      <c r="C867" s="14"/>
-      <c r="D867" s="20"/>
-      <c r="E867" s="15"/>
-      <c r="F867" s="15"/>
-      <c r="G867" s="15"/>
+      <c r="B867" s="8">
+        <v>26390.0</v>
+      </c>
+      <c r="C867" s="14">
+        <v>26390.0</v>
+      </c>
+      <c r="D867" s="9" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E867" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F867" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G867" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H867" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I867" s="21"/>
-      <c r="J867" s="21"/>
+      <c r="I867" s="11">
+        <v>46301.0</v>
+      </c>
+      <c r="J867" s="11">
+        <v>46301.0</v>
+      </c>
       <c r="K867" s="10" t="s">
         <v>20</v>
       </c>
@@ -42198,17 +42805,33 @@
     </row>
     <row r="868" ht="18.0" customHeight="1">
       <c r="A868" s="6"/>
-      <c r="B868" s="17"/>
-      <c r="C868" s="14"/>
-      <c r="D868" s="20"/>
-      <c r="E868" s="15"/>
-      <c r="F868" s="15"/>
-      <c r="G868" s="15"/>
+      <c r="B868" s="8">
+        <v>29628.0</v>
+      </c>
+      <c r="C868" s="14">
+        <v>29628.0</v>
+      </c>
+      <c r="D868" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="E868" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="F868" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G868" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H868" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I868" s="21"/>
-      <c r="J868" s="21"/>
+      <c r="I868" s="11">
+        <v>46291.0</v>
+      </c>
+      <c r="J868" s="11">
+        <v>46291.0</v>
+      </c>
       <c r="K868" s="10" t="s">
         <v>20</v>
       </c>
@@ -42224,17 +42847,33 @@
     </row>
     <row r="869" ht="18.0" customHeight="1">
       <c r="A869" s="6"/>
-      <c r="B869" s="17"/>
-      <c r="C869" s="14"/>
-      <c r="D869" s="20"/>
-      <c r="E869" s="15"/>
-      <c r="F869" s="15"/>
-      <c r="G869" s="15"/>
+      <c r="B869" s="8">
+        <v>29448.0</v>
+      </c>
+      <c r="C869" s="14">
+        <v>29448.0</v>
+      </c>
+      <c r="D869" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="E869" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="F869" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G869" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H869" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I869" s="21"/>
-      <c r="J869" s="21"/>
+      <c r="I869" s="11">
+        <v>46282.0</v>
+      </c>
+      <c r="J869" s="11">
+        <v>46282.0</v>
+      </c>
       <c r="K869" s="10" t="s">
         <v>20</v>
       </c>
@@ -42250,17 +42889,33 @@
     </row>
     <row r="870" ht="18.0" customHeight="1">
       <c r="A870" s="6"/>
-      <c r="B870" s="17"/>
-      <c r="C870" s="14"/>
-      <c r="D870" s="20"/>
-      <c r="E870" s="15"/>
-      <c r="F870" s="15"/>
-      <c r="G870" s="15"/>
+      <c r="B870" s="8">
+        <v>23613.0</v>
+      </c>
+      <c r="C870" s="14">
+        <v>23613.0</v>
+      </c>
+      <c r="D870" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="E870" s="16" t="s">
+        <v>721</v>
+      </c>
+      <c r="F870" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G870" s="18" t="s">
+        <v>1294</v>
+      </c>
       <c r="H870" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I870" s="21"/>
-      <c r="J870" s="21"/>
+      <c r="I870" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J870" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K870" s="10" t="s">
         <v>20</v>
       </c>
@@ -42276,17 +42931,33 @@
     </row>
     <row r="871" ht="18.0" customHeight="1">
       <c r="A871" s="6"/>
-      <c r="B871" s="17"/>
-      <c r="C871" s="14"/>
-      <c r="D871" s="20"/>
-      <c r="E871" s="15"/>
-      <c r="F871" s="15"/>
-      <c r="G871" s="15"/>
+      <c r="B871" s="8">
+        <v>30361.0</v>
+      </c>
+      <c r="C871" s="14">
+        <v>30361.0</v>
+      </c>
+      <c r="D871" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E871" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="F871" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G871" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H871" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I871" s="21"/>
-      <c r="J871" s="21"/>
+      <c r="I871" s="11">
+        <v>46294.0</v>
+      </c>
+      <c r="J871" s="11">
+        <v>46294.0</v>
+      </c>
       <c r="K871" s="10" t="s">
         <v>20</v>
       </c>
@@ -42302,17 +42973,33 @@
     </row>
     <row r="872" ht="18.0" customHeight="1">
       <c r="A872" s="6"/>
-      <c r="B872" s="17"/>
-      <c r="C872" s="14"/>
-      <c r="D872" s="20"/>
-      <c r="E872" s="15"/>
-      <c r="F872" s="15"/>
-      <c r="G872" s="15"/>
+      <c r="B872" s="8">
+        <v>30361.0</v>
+      </c>
+      <c r="C872" s="14">
+        <v>30361.0</v>
+      </c>
+      <c r="D872" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E872" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="F872" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G872" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H872" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I872" s="21"/>
-      <c r="J872" s="21"/>
+      <c r="I872" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J872" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K872" s="10" t="s">
         <v>20</v>
       </c>
@@ -42328,17 +43015,33 @@
     </row>
     <row r="873" ht="18.0" customHeight="1">
       <c r="A873" s="6"/>
-      <c r="B873" s="17"/>
-      <c r="C873" s="14"/>
-      <c r="D873" s="20"/>
-      <c r="E873" s="15"/>
-      <c r="F873" s="15"/>
-      <c r="G873" s="15"/>
+      <c r="B873" s="8">
+        <v>27941.0</v>
+      </c>
+      <c r="C873" s="14">
+        <v>27941.0</v>
+      </c>
+      <c r="D873" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="E873" s="16" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F873" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G873" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H873" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I873" s="21"/>
-      <c r="J873" s="21"/>
+      <c r="I873" s="11">
+        <v>46301.0</v>
+      </c>
+      <c r="J873" s="11">
+        <v>46301.0</v>
+      </c>
       <c r="K873" s="10" t="s">
         <v>20</v>
       </c>
@@ -42354,17 +43057,33 @@
     </row>
     <row r="874" ht="18.0" customHeight="1">
       <c r="A874" s="6"/>
-      <c r="B874" s="17"/>
-      <c r="C874" s="14"/>
-      <c r="D874" s="20"/>
-      <c r="E874" s="15"/>
-      <c r="F874" s="15"/>
-      <c r="G874" s="15"/>
+      <c r="B874" s="8">
+        <v>30361.0</v>
+      </c>
+      <c r="C874" s="14">
+        <v>30361.0</v>
+      </c>
+      <c r="D874" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E874" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="F874" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G874" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H874" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I874" s="21"/>
-      <c r="J874" s="21"/>
+      <c r="I874" s="11">
+        <v>46286.0</v>
+      </c>
+      <c r="J874" s="11">
+        <v>46287.0</v>
+      </c>
       <c r="K874" s="10" t="s">
         <v>20</v>
       </c>
@@ -42380,17 +43099,33 @@
     </row>
     <row r="875" ht="18.0" customHeight="1">
       <c r="A875" s="6"/>
-      <c r="B875" s="17"/>
-      <c r="C875" s="14"/>
-      <c r="D875" s="20"/>
-      <c r="E875" s="15"/>
-      <c r="F875" s="15"/>
-      <c r="G875" s="15"/>
+      <c r="B875" s="8">
+        <v>31283.0</v>
+      </c>
+      <c r="C875" s="14">
+        <v>31283.0</v>
+      </c>
+      <c r="D875" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E875" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="F875" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G875" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H875" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I875" s="21"/>
-      <c r="J875" s="21"/>
+      <c r="I875" s="11">
+        <v>46282.0</v>
+      </c>
+      <c r="J875" s="11">
+        <v>46282.0</v>
+      </c>
       <c r="K875" s="10" t="s">
         <v>20</v>
       </c>
@@ -42406,17 +43141,33 @@
     </row>
     <row r="876" ht="18.0" customHeight="1">
       <c r="A876" s="6"/>
-      <c r="B876" s="17"/>
-      <c r="C876" s="14"/>
-      <c r="D876" s="20"/>
-      <c r="E876" s="15"/>
-      <c r="F876" s="15"/>
-      <c r="G876" s="15"/>
+      <c r="B876" s="8">
+        <v>31283.0</v>
+      </c>
+      <c r="C876" s="14">
+        <v>31283.0</v>
+      </c>
+      <c r="D876" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E876" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="F876" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G876" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H876" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I876" s="21"/>
-      <c r="J876" s="21"/>
+      <c r="I876" s="11">
+        <v>46277.0</v>
+      </c>
+      <c r="J876" s="11">
+        <v>46277.0</v>
+      </c>
       <c r="K876" s="10" t="s">
         <v>20</v>
       </c>
@@ -42432,17 +43183,33 @@
     </row>
     <row r="877" ht="18.0" customHeight="1">
       <c r="A877" s="6"/>
-      <c r="B877" s="17"/>
-      <c r="C877" s="14"/>
-      <c r="D877" s="20"/>
-      <c r="E877" s="15"/>
-      <c r="F877" s="15"/>
-      <c r="G877" s="15"/>
+      <c r="B877" s="8">
+        <v>31283.0</v>
+      </c>
+      <c r="C877" s="14">
+        <v>31283.0</v>
+      </c>
+      <c r="D877" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E877" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="F877" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G877" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H877" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I877" s="21"/>
-      <c r="J877" s="21"/>
+      <c r="I877" s="11">
+        <v>46294.0</v>
+      </c>
+      <c r="J877" s="11">
+        <v>46294.0</v>
+      </c>
       <c r="K877" s="10" t="s">
         <v>20</v>
       </c>
@@ -42458,17 +43225,33 @@
     </row>
     <row r="878" ht="18.0" customHeight="1">
       <c r="A878" s="6"/>
-      <c r="B878" s="17"/>
-      <c r="C878" s="14"/>
-      <c r="D878" s="20"/>
-      <c r="E878" s="15"/>
-      <c r="F878" s="15"/>
-      <c r="G878" s="15"/>
+      <c r="B878" s="8">
+        <v>31283.0</v>
+      </c>
+      <c r="C878" s="14">
+        <v>31283.0</v>
+      </c>
+      <c r="D878" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E878" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="F878" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G878" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H878" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I878" s="21"/>
-      <c r="J878" s="21"/>
+      <c r="I878" s="11">
+        <v>46295.0</v>
+      </c>
+      <c r="J878" s="11">
+        <v>46295.0</v>
+      </c>
       <c r="K878" s="10" t="s">
         <v>20</v>
       </c>
@@ -42484,17 +43267,33 @@
     </row>
     <row r="879" ht="18.0" customHeight="1">
       <c r="A879" s="6"/>
-      <c r="B879" s="17"/>
-      <c r="C879" s="14"/>
-      <c r="D879" s="20"/>
-      <c r="E879" s="15"/>
-      <c r="F879" s="15"/>
-      <c r="G879" s="15"/>
+      <c r="B879" s="8">
+        <v>31283.0</v>
+      </c>
+      <c r="C879" s="14">
+        <v>31283.0</v>
+      </c>
+      <c r="D879" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E879" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="F879" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G879" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H879" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I879" s="21"/>
-      <c r="J879" s="21"/>
+      <c r="I879" s="11">
+        <v>46302.0</v>
+      </c>
+      <c r="J879" s="11">
+        <v>46302.0</v>
+      </c>
       <c r="K879" s="10" t="s">
         <v>20</v>
       </c>
@@ -42510,17 +43309,33 @@
     </row>
     <row r="880" ht="18.0" customHeight="1">
       <c r="A880" s="6"/>
-      <c r="B880" s="17"/>
-      <c r="C880" s="14"/>
-      <c r="D880" s="20"/>
-      <c r="E880" s="15"/>
-      <c r="F880" s="15"/>
-      <c r="G880" s="15"/>
+      <c r="B880" s="8">
+        <v>28875.0</v>
+      </c>
+      <c r="C880" s="14">
+        <v>28875.0</v>
+      </c>
+      <c r="D880" s="9" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E880" s="16" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F880" s="16" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G880" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H880" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I880" s="21"/>
-      <c r="J880" s="21"/>
+      <c r="I880" s="11">
+        <v>46308.0</v>
+      </c>
+      <c r="J880" s="11">
+        <v>46309.0</v>
+      </c>
       <c r="K880" s="10" t="s">
         <v>20</v>
       </c>
@@ -42536,17 +43351,33 @@
     </row>
     <row r="881" ht="18.0" customHeight="1">
       <c r="A881" s="6"/>
-      <c r="B881" s="17"/>
-      <c r="C881" s="14"/>
-      <c r="D881" s="20"/>
-      <c r="E881" s="15"/>
-      <c r="F881" s="15"/>
-      <c r="G881" s="15"/>
+      <c r="B881" s="8">
+        <v>28875.0</v>
+      </c>
+      <c r="C881" s="14">
+        <v>28875.0</v>
+      </c>
+      <c r="D881" s="9" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E881" s="16" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F881" s="16" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G881" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H881" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I881" s="21"/>
-      <c r="J881" s="21"/>
+      <c r="I881" s="11">
+        <v>46306.0</v>
+      </c>
+      <c r="J881" s="11">
+        <v>46307.0</v>
+      </c>
       <c r="K881" s="10" t="s">
         <v>20</v>
       </c>
@@ -42562,17 +43393,33 @@
     </row>
     <row r="882" ht="18.0" customHeight="1">
       <c r="A882" s="6"/>
-      <c r="B882" s="17"/>
-      <c r="C882" s="14"/>
-      <c r="D882" s="20"/>
-      <c r="E882" s="15"/>
-      <c r="F882" s="15"/>
-      <c r="G882" s="15"/>
+      <c r="B882" s="8">
+        <v>27164.0</v>
+      </c>
+      <c r="C882" s="14">
+        <v>27164.0</v>
+      </c>
+      <c r="D882" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E882" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="F882" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G882" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H882" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I882" s="21"/>
-      <c r="J882" s="21"/>
+      <c r="I882" s="11">
+        <v>46310.0</v>
+      </c>
+      <c r="J882" s="11">
+        <v>46310.0</v>
+      </c>
       <c r="K882" s="10" t="s">
         <v>20</v>
       </c>
@@ -42588,17 +43435,33 @@
     </row>
     <row r="883" ht="18.0" customHeight="1">
       <c r="A883" s="6"/>
-      <c r="B883" s="17"/>
-      <c r="C883" s="14"/>
-      <c r="D883" s="20"/>
-      <c r="E883" s="15"/>
-      <c r="F883" s="15"/>
-      <c r="G883" s="15"/>
+      <c r="B883" s="8">
+        <v>32391.0</v>
+      </c>
+      <c r="C883" s="14">
+        <v>32391.0</v>
+      </c>
+      <c r="D883" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E883" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="F883" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="G883" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H883" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I883" s="21"/>
-      <c r="J883" s="21"/>
+      <c r="I883" s="11">
+        <v>46308.0</v>
+      </c>
+      <c r="J883" s="11">
+        <v>46308.0</v>
+      </c>
       <c r="K883" s="10" t="s">
         <v>20</v>
       </c>
@@ -42614,17 +43477,33 @@
     </row>
     <row r="884" ht="18.0" customHeight="1">
       <c r="A884" s="6"/>
-      <c r="B884" s="17"/>
-      <c r="C884" s="14"/>
-      <c r="D884" s="20"/>
-      <c r="E884" s="15"/>
-      <c r="F884" s="15"/>
-      <c r="G884" s="15"/>
+      <c r="B884" s="8">
+        <v>31304.0</v>
+      </c>
+      <c r="C884" s="14">
+        <v>31304.0</v>
+      </c>
+      <c r="D884" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="E884" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="F884" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G884" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H884" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I884" s="21"/>
-      <c r="J884" s="21"/>
+      <c r="I884" s="11">
+        <v>46302.0</v>
+      </c>
+      <c r="J884" s="11">
+        <v>46302.0</v>
+      </c>
       <c r="K884" s="10" t="s">
         <v>20</v>
       </c>
@@ -42640,17 +43519,33 @@
     </row>
     <row r="885" ht="18.0" customHeight="1">
       <c r="A885" s="6"/>
-      <c r="B885" s="17"/>
-      <c r="C885" s="14"/>
-      <c r="D885" s="20"/>
-      <c r="E885" s="15"/>
-      <c r="F885" s="15"/>
-      <c r="G885" s="15"/>
+      <c r="B885" s="8">
+        <v>30646.0</v>
+      </c>
+      <c r="C885" s="14">
+        <v>30646.0</v>
+      </c>
+      <c r="D885" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="E885" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="F885" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G885" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H885" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I885" s="21"/>
-      <c r="J885" s="21"/>
+      <c r="I885" s="11">
+        <v>46296.0</v>
+      </c>
+      <c r="J885" s="11">
+        <v>46296.0</v>
+      </c>
       <c r="K885" s="10" t="s">
         <v>20</v>
       </c>
@@ -42666,17 +43561,33 @@
     </row>
     <row r="886" ht="18.0" customHeight="1">
       <c r="A886" s="6"/>
-      <c r="B886" s="17"/>
-      <c r="C886" s="14"/>
-      <c r="D886" s="20"/>
-      <c r="E886" s="15"/>
-      <c r="F886" s="15"/>
-      <c r="G886" s="15"/>
+      <c r="B886" s="8">
+        <v>31720.0</v>
+      </c>
+      <c r="C886" s="14">
+        <v>31720.0</v>
+      </c>
+      <c r="D886" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="E886" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="F886" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G886" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H886" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I886" s="21"/>
-      <c r="J886" s="21"/>
+      <c r="I886" s="11">
+        <v>46292.0</v>
+      </c>
+      <c r="J886" s="11">
+        <v>46292.0</v>
+      </c>
       <c r="K886" s="10" t="s">
         <v>20</v>
       </c>
@@ -42692,17 +43603,33 @@
     </row>
     <row r="887" ht="18.0" customHeight="1">
       <c r="A887" s="6"/>
-      <c r="B887" s="17"/>
-      <c r="C887" s="14"/>
-      <c r="D887" s="20"/>
-      <c r="E887" s="15"/>
-      <c r="F887" s="15"/>
-      <c r="G887" s="15"/>
+      <c r="B887" s="8">
+        <v>31720.0</v>
+      </c>
+      <c r="C887" s="14">
+        <v>31720.0</v>
+      </c>
+      <c r="D887" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="E887" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="F887" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G887" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H887" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I887" s="21"/>
-      <c r="J887" s="21"/>
+      <c r="I887" s="11">
+        <v>46291.0</v>
+      </c>
+      <c r="J887" s="11">
+        <v>46291.0</v>
+      </c>
       <c r="K887" s="10" t="s">
         <v>20</v>
       </c>
@@ -42718,17 +43645,33 @@
     </row>
     <row r="888" ht="18.0" customHeight="1">
       <c r="A888" s="6"/>
-      <c r="B888" s="17"/>
-      <c r="C888" s="14"/>
-      <c r="D888" s="20"/>
-      <c r="E888" s="15"/>
-      <c r="F888" s="15"/>
-      <c r="G888" s="15"/>
+      <c r="B888" s="8">
+        <v>31720.0</v>
+      </c>
+      <c r="C888" s="14">
+        <v>31720.0</v>
+      </c>
+      <c r="D888" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="E888" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="F888" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G888" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H888" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I888" s="21"/>
-      <c r="J888" s="21"/>
+      <c r="I888" s="11">
+        <v>46284.0</v>
+      </c>
+      <c r="J888" s="11">
+        <v>46284.0</v>
+      </c>
       <c r="K888" s="10" t="s">
         <v>20</v>
       </c>
@@ -42744,17 +43687,33 @@
     </row>
     <row r="889" ht="18.0" customHeight="1">
       <c r="A889" s="6"/>
-      <c r="B889" s="17"/>
-      <c r="C889" s="14"/>
-      <c r="D889" s="20"/>
-      <c r="E889" s="15"/>
-      <c r="F889" s="15"/>
-      <c r="G889" s="15"/>
+      <c r="B889" s="8">
+        <v>31720.0</v>
+      </c>
+      <c r="C889" s="14">
+        <v>31720.0</v>
+      </c>
+      <c r="D889" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="E889" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="F889" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G889" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H889" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I889" s="21"/>
-      <c r="J889" s="21"/>
+      <c r="I889" s="11">
+        <v>46280.0</v>
+      </c>
+      <c r="J889" s="11">
+        <v>46280.0</v>
+      </c>
       <c r="K889" s="10" t="s">
         <v>20</v>
       </c>
@@ -42770,17 +43729,33 @@
     </row>
     <row r="890" ht="18.0" customHeight="1">
       <c r="A890" s="6"/>
-      <c r="B890" s="17"/>
-      <c r="C890" s="14"/>
-      <c r="D890" s="20"/>
-      <c r="E890" s="15"/>
-      <c r="F890" s="15"/>
-      <c r="G890" s="15"/>
+      <c r="B890" s="8">
+        <v>31720.0</v>
+      </c>
+      <c r="C890" s="14">
+        <v>31720.0</v>
+      </c>
+      <c r="D890" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="E890" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="F890" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G890" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H890" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I890" s="21"/>
-      <c r="J890" s="21"/>
+      <c r="I890" s="11">
+        <v>46277.0</v>
+      </c>
+      <c r="J890" s="11">
+        <v>46277.0</v>
+      </c>
       <c r="K890" s="10" t="s">
         <v>20</v>
       </c>
@@ -42796,17 +43771,33 @@
     </row>
     <row r="891" ht="18.0" customHeight="1">
       <c r="A891" s="6"/>
-      <c r="B891" s="17"/>
-      <c r="C891" s="14"/>
-      <c r="D891" s="20"/>
-      <c r="E891" s="15"/>
-      <c r="F891" s="15"/>
-      <c r="G891" s="15"/>
+      <c r="B891" s="8">
+        <v>30858.0</v>
+      </c>
+      <c r="C891" s="14">
+        <v>30858.0</v>
+      </c>
+      <c r="D891" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E891" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="F891" s="16" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G891" s="18" t="s">
+        <v>1327</v>
+      </c>
       <c r="H891" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I891" s="21"/>
-      <c r="J891" s="21"/>
+      <c r="I891" s="11">
+        <v>46287.0</v>
+      </c>
+      <c r="J891" s="11">
+        <v>46287.0</v>
+      </c>
       <c r="K891" s="10" t="s">
         <v>20</v>
       </c>
@@ -42822,17 +43813,33 @@
     </row>
     <row r="892" ht="18.0" customHeight="1">
       <c r="A892" s="6"/>
-      <c r="B892" s="17"/>
-      <c r="C892" s="14"/>
-      <c r="D892" s="20"/>
-      <c r="E892" s="15"/>
-      <c r="F892" s="15"/>
-      <c r="G892" s="15"/>
+      <c r="B892" s="8">
+        <v>30858.0</v>
+      </c>
+      <c r="C892" s="14">
+        <v>30858.0</v>
+      </c>
+      <c r="D892" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E892" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="F892" s="16" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G892" s="18" t="s">
+        <v>1327</v>
+      </c>
       <c r="H892" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I892" s="21"/>
-      <c r="J892" s="21"/>
+      <c r="I892" s="11">
+        <v>46302.0</v>
+      </c>
+      <c r="J892" s="11">
+        <v>46302.0</v>
+      </c>
       <c r="K892" s="10" t="s">
         <v>20</v>
       </c>
@@ -42848,17 +43855,33 @@
     </row>
     <row r="893" ht="18.0" customHeight="1">
       <c r="A893" s="6"/>
-      <c r="B893" s="17"/>
-      <c r="C893" s="14"/>
-      <c r="D893" s="20"/>
-      <c r="E893" s="15"/>
-      <c r="F893" s="15"/>
-      <c r="G893" s="15"/>
+      <c r="B893" s="8">
+        <v>30858.0</v>
+      </c>
+      <c r="C893" s="14">
+        <v>30858.0</v>
+      </c>
+      <c r="D893" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E893" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="F893" s="16" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G893" s="18" t="s">
+        <v>1327</v>
+      </c>
       <c r="H893" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I893" s="21"/>
-      <c r="J893" s="21"/>
+      <c r="I893" s="11">
+        <v>46278.0</v>
+      </c>
+      <c r="J893" s="11">
+        <v>46278.0</v>
+      </c>
       <c r="K893" s="10" t="s">
         <v>20</v>
       </c>
@@ -42874,17 +43897,33 @@
     </row>
     <row r="894" ht="18.0" customHeight="1">
       <c r="A894" s="6"/>
-      <c r="B894" s="17"/>
-      <c r="C894" s="14"/>
-      <c r="D894" s="20"/>
-      <c r="E894" s="15"/>
-      <c r="F894" s="15"/>
-      <c r="G894" s="15"/>
+      <c r="B894" s="8">
+        <v>30574.0</v>
+      </c>
+      <c r="C894" s="14">
+        <v>30574.0</v>
+      </c>
+      <c r="D894" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E894" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="F894" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G894" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H894" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I894" s="21"/>
-      <c r="J894" s="21"/>
+      <c r="I894" s="11">
+        <v>46291.0</v>
+      </c>
+      <c r="J894" s="11">
+        <v>46291.0</v>
+      </c>
       <c r="K894" s="10" t="s">
         <v>20</v>
       </c>
@@ -42900,17 +43939,33 @@
     </row>
     <row r="895" ht="18.0" customHeight="1">
       <c r="A895" s="6"/>
-      <c r="B895" s="17"/>
-      <c r="C895" s="14"/>
-      <c r="D895" s="20"/>
-      <c r="E895" s="15"/>
-      <c r="F895" s="15"/>
-      <c r="G895" s="15"/>
+      <c r="B895" s="8">
+        <v>30574.0</v>
+      </c>
+      <c r="C895" s="14">
+        <v>30574.0</v>
+      </c>
+      <c r="D895" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E895" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="F895" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G895" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H895" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I895" s="21"/>
-      <c r="J895" s="21"/>
+      <c r="I895" s="11">
+        <v>46284.0</v>
+      </c>
+      <c r="J895" s="11">
+        <v>46284.0</v>
+      </c>
       <c r="K895" s="10" t="s">
         <v>20</v>
       </c>
@@ -42926,17 +43981,33 @@
     </row>
     <row r="896" ht="18.0" customHeight="1">
       <c r="A896" s="6"/>
-      <c r="B896" s="17"/>
-      <c r="C896" s="14"/>
-      <c r="D896" s="20"/>
-      <c r="E896" s="15"/>
-      <c r="F896" s="15"/>
-      <c r="G896" s="15"/>
+      <c r="B896" s="8">
+        <v>30574.0</v>
+      </c>
+      <c r="C896" s="14">
+        <v>30574.0</v>
+      </c>
+      <c r="D896" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E896" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="F896" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G896" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H896" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I896" s="21"/>
-      <c r="J896" s="21"/>
+      <c r="I896" s="11">
+        <v>46280.0</v>
+      </c>
+      <c r="J896" s="11">
+        <v>46280.0</v>
+      </c>
       <c r="K896" s="10" t="s">
         <v>20</v>
       </c>
@@ -42952,17 +44023,33 @@
     </row>
     <row r="897" ht="18.0" customHeight="1">
       <c r="A897" s="6"/>
-      <c r="B897" s="17"/>
-      <c r="C897" s="14"/>
-      <c r="D897" s="20"/>
-      <c r="E897" s="15"/>
-      <c r="F897" s="15"/>
-      <c r="G897" s="15"/>
+      <c r="B897" s="8">
+        <v>28211.0</v>
+      </c>
+      <c r="C897" s="14">
+        <v>28211.0</v>
+      </c>
+      <c r="D897" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E897" s="16" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F897" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G897" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H897" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I897" s="21"/>
-      <c r="J897" s="21"/>
+      <c r="I897" s="11">
+        <v>46278.0</v>
+      </c>
+      <c r="J897" s="11">
+        <v>46278.0</v>
+      </c>
       <c r="K897" s="10" t="s">
         <v>20</v>
       </c>
@@ -42978,17 +44065,33 @@
     </row>
     <row r="898" ht="18.0" customHeight="1">
       <c r="A898" s="6"/>
-      <c r="B898" s="17"/>
-      <c r="C898" s="14"/>
-      <c r="D898" s="20"/>
-      <c r="E898" s="15"/>
-      <c r="F898" s="15"/>
-      <c r="G898" s="15"/>
+      <c r="B898" s="8">
+        <v>28211.0</v>
+      </c>
+      <c r="C898" s="14">
+        <v>28211.0</v>
+      </c>
+      <c r="D898" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E898" s="16" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F898" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G898" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H898" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I898" s="21"/>
-      <c r="J898" s="21"/>
+      <c r="I898" s="11">
+        <v>46279.0</v>
+      </c>
+      <c r="J898" s="11">
+        <v>46280.0</v>
+      </c>
       <c r="K898" s="10" t="s">
         <v>20</v>
       </c>
@@ -43004,17 +44107,33 @@
     </row>
     <row r="899" ht="18.0" customHeight="1">
       <c r="A899" s="6"/>
-      <c r="B899" s="17"/>
-      <c r="C899" s="14"/>
-      <c r="D899" s="20"/>
-      <c r="E899" s="15"/>
-      <c r="F899" s="15"/>
-      <c r="G899" s="15"/>
+      <c r="B899" s="8">
+        <v>28211.0</v>
+      </c>
+      <c r="C899" s="14">
+        <v>28211.0</v>
+      </c>
+      <c r="D899" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E899" s="16" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F899" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G899" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H899" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I899" s="21"/>
-      <c r="J899" s="21"/>
+      <c r="I899" s="11">
+        <v>46281.0</v>
+      </c>
+      <c r="J899" s="11">
+        <v>46281.0</v>
+      </c>
       <c r="K899" s="10" t="s">
         <v>20</v>
       </c>
@@ -43030,17 +44149,33 @@
     </row>
     <row r="900" ht="18.0" customHeight="1">
       <c r="A900" s="6"/>
-      <c r="B900" s="17"/>
-      <c r="C900" s="14"/>
-      <c r="D900" s="20"/>
-      <c r="E900" s="15"/>
-      <c r="F900" s="15"/>
-      <c r="G900" s="15"/>
+      <c r="B900" s="8">
+        <v>28211.0</v>
+      </c>
+      <c r="C900" s="14">
+        <v>28211.0</v>
+      </c>
+      <c r="D900" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E900" s="16" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F900" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G900" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H900" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I900" s="21"/>
-      <c r="J900" s="21"/>
+      <c r="I900" s="11">
+        <v>46286.0</v>
+      </c>
+      <c r="J900" s="11">
+        <v>46286.0</v>
+      </c>
       <c r="K900" s="10" t="s">
         <v>20</v>
       </c>
@@ -43056,17 +44191,33 @@
     </row>
     <row r="901" ht="18.0" customHeight="1">
       <c r="A901" s="6"/>
-      <c r="B901" s="17"/>
-      <c r="C901" s="14"/>
-      <c r="D901" s="20"/>
-      <c r="E901" s="15"/>
-      <c r="F901" s="15"/>
-      <c r="G901" s="15"/>
+      <c r="B901" s="8">
+        <v>29756.0</v>
+      </c>
+      <c r="C901" s="14">
+        <v>29756.0</v>
+      </c>
+      <c r="D901" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="E901" s="16" t="s">
+        <v>744</v>
+      </c>
+      <c r="F901" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G901" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H901" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I901" s="21"/>
-      <c r="J901" s="21"/>
+      <c r="I901" s="11">
+        <v>46298.0</v>
+      </c>
+      <c r="J901" s="11">
+        <v>46298.0</v>
+      </c>
       <c r="K901" s="10" t="s">
         <v>20</v>
       </c>
@@ -43082,17 +44233,33 @@
     </row>
     <row r="902" ht="18.0" customHeight="1">
       <c r="A902" s="6"/>
-      <c r="B902" s="17"/>
-      <c r="C902" s="14"/>
-      <c r="D902" s="20"/>
-      <c r="E902" s="15"/>
-      <c r="F902" s="15"/>
-      <c r="G902" s="15"/>
+      <c r="B902" s="8">
+        <v>27864.0</v>
+      </c>
+      <c r="C902" s="14">
+        <v>27864.0</v>
+      </c>
+      <c r="D902" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="E902" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="F902" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G902" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H902" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I902" s="21"/>
-      <c r="J902" s="21"/>
+      <c r="I902" s="11">
+        <v>46282.0</v>
+      </c>
+      <c r="J902" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K902" s="10" t="s">
         <v>20</v>
       </c>
@@ -43108,17 +44275,33 @@
     </row>
     <row r="903" ht="18.0" customHeight="1">
       <c r="A903" s="6"/>
-      <c r="B903" s="17"/>
-      <c r="C903" s="14"/>
-      <c r="D903" s="20"/>
-      <c r="E903" s="15"/>
-      <c r="F903" s="15"/>
-      <c r="G903" s="15"/>
+      <c r="B903" s="8">
+        <v>28215.0</v>
+      </c>
+      <c r="C903" s="14">
+        <v>28215.0</v>
+      </c>
+      <c r="D903" s="9" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E903" s="16" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F903" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G903" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H903" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I903" s="21"/>
-      <c r="J903" s="21"/>
+      <c r="I903" s="11">
+        <v>46279.0</v>
+      </c>
+      <c r="J903" s="11">
+        <v>46279.0</v>
+      </c>
       <c r="K903" s="10" t="s">
         <v>20</v>
       </c>
@@ -43134,17 +44317,33 @@
     </row>
     <row r="904" ht="18.0" customHeight="1">
       <c r="A904" s="6"/>
-      <c r="B904" s="17"/>
-      <c r="C904" s="14"/>
-      <c r="D904" s="20"/>
-      <c r="E904" s="15"/>
-      <c r="F904" s="15"/>
-      <c r="G904" s="15"/>
+      <c r="B904" s="8">
+        <v>31279.0</v>
+      </c>
+      <c r="C904" s="14">
+        <v>31279.0</v>
+      </c>
+      <c r="D904" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E904" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F904" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G904" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H904" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I904" s="21"/>
-      <c r="J904" s="21"/>
+      <c r="I904" s="11">
+        <v>46302.0</v>
+      </c>
+      <c r="J904" s="11">
+        <v>46302.0</v>
+      </c>
       <c r="K904" s="10" t="s">
         <v>20</v>
       </c>
@@ -43160,17 +44359,33 @@
     </row>
     <row r="905" ht="18.0" customHeight="1">
       <c r="A905" s="6"/>
-      <c r="B905" s="17"/>
-      <c r="C905" s="14"/>
-      <c r="D905" s="20"/>
-      <c r="E905" s="15"/>
-      <c r="F905" s="15"/>
-      <c r="G905" s="15"/>
+      <c r="B905" s="8">
+        <v>31279.0</v>
+      </c>
+      <c r="C905" s="14">
+        <v>31279.0</v>
+      </c>
+      <c r="D905" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E905" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F905" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G905" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H905" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I905" s="21"/>
-      <c r="J905" s="21"/>
+      <c r="I905" s="11">
+        <v>46298.0</v>
+      </c>
+      <c r="J905" s="11">
+        <v>46298.0</v>
+      </c>
       <c r="K905" s="10" t="s">
         <v>20</v>
       </c>
@@ -43186,17 +44401,33 @@
     </row>
     <row r="906" ht="18.0" customHeight="1">
       <c r="A906" s="6"/>
-      <c r="B906" s="17"/>
-      <c r="C906" s="14"/>
-      <c r="D906" s="20"/>
-      <c r="E906" s="15"/>
-      <c r="F906" s="15"/>
-      <c r="G906" s="15"/>
+      <c r="B906" s="8">
+        <v>31279.0</v>
+      </c>
+      <c r="C906" s="14">
+        <v>31279.0</v>
+      </c>
+      <c r="D906" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E906" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F906" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G906" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H906" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I906" s="21"/>
-      <c r="J906" s="21"/>
+      <c r="I906" s="11">
+        <v>46292.0</v>
+      </c>
+      <c r="J906" s="11">
+        <v>46292.0</v>
+      </c>
       <c r="K906" s="10" t="s">
         <v>20</v>
       </c>
@@ -43212,17 +44443,33 @@
     </row>
     <row r="907" ht="18.0" customHeight="1">
       <c r="A907" s="6"/>
-      <c r="B907" s="17"/>
-      <c r="C907" s="14"/>
-      <c r="D907" s="20"/>
-      <c r="E907" s="15"/>
-      <c r="F907" s="15"/>
-      <c r="G907" s="15"/>
+      <c r="B907" s="8">
+        <v>31279.0</v>
+      </c>
+      <c r="C907" s="14">
+        <v>31279.0</v>
+      </c>
+      <c r="D907" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E907" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F907" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G907" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H907" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I907" s="21"/>
-      <c r="J907" s="21"/>
+      <c r="I907" s="11">
+        <v>46278.0</v>
+      </c>
+      <c r="J907" s="11">
+        <v>46278.0</v>
+      </c>
       <c r="K907" s="10" t="s">
         <v>20</v>
       </c>
@@ -43238,17 +44485,33 @@
     </row>
     <row r="908" ht="18.0" customHeight="1">
       <c r="A908" s="6"/>
-      <c r="B908" s="17"/>
-      <c r="C908" s="14"/>
-      <c r="D908" s="20"/>
-      <c r="E908" s="15"/>
-      <c r="F908" s="15"/>
-      <c r="G908" s="15"/>
+      <c r="B908" s="8">
+        <v>31279.0</v>
+      </c>
+      <c r="C908" s="14">
+        <v>31279.0</v>
+      </c>
+      <c r="D908" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="E908" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F908" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G908" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H908" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I908" s="21"/>
-      <c r="J908" s="21"/>
+      <c r="I908" s="11">
+        <v>46277.0</v>
+      </c>
+      <c r="J908" s="11">
+        <v>46277.0</v>
+      </c>
       <c r="K908" s="10" t="s">
         <v>20</v>
       </c>
@@ -43264,17 +44527,29 @@
     </row>
     <row r="909" ht="18.0" customHeight="1">
       <c r="A909" s="6"/>
-      <c r="B909" s="17"/>
-      <c r="C909" s="14"/>
-      <c r="D909" s="20"/>
-      <c r="E909" s="15"/>
-      <c r="F909" s="15"/>
-      <c r="G909" s="15"/>
+      <c r="B909" s="8">
+        <v>31271.0</v>
+      </c>
+      <c r="C909" s="14">
+        <v>31271.0</v>
+      </c>
+      <c r="D909" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="E909" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="F909" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G909" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H909" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I909" s="21"/>
-      <c r="J909" s="21"/>
+      <c r="I909" s="20"/>
+      <c r="J909" s="20"/>
       <c r="K909" s="10" t="s">
         <v>20</v>
       </c>
@@ -43290,17 +44565,29 @@
     </row>
     <row r="910" ht="18.0" customHeight="1">
       <c r="A910" s="6"/>
-      <c r="B910" s="17"/>
-      <c r="C910" s="14"/>
-      <c r="D910" s="20"/>
-      <c r="E910" s="15"/>
-      <c r="F910" s="15"/>
-      <c r="G910" s="15"/>
+      <c r="B910" s="8">
+        <v>31271.0</v>
+      </c>
+      <c r="C910" s="14">
+        <v>31271.0</v>
+      </c>
+      <c r="D910" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="E910" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="F910" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G910" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H910" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I910" s="21"/>
-      <c r="J910" s="21"/>
+      <c r="I910" s="20"/>
+      <c r="J910" s="20"/>
       <c r="K910" s="10" t="s">
         <v>20</v>
       </c>
@@ -43316,17 +44603,33 @@
     </row>
     <row r="911" ht="18.0" customHeight="1">
       <c r="A911" s="6"/>
-      <c r="B911" s="17"/>
-      <c r="C911" s="14"/>
-      <c r="D911" s="20"/>
-      <c r="E911" s="15"/>
-      <c r="F911" s="15"/>
-      <c r="G911" s="15"/>
+      <c r="B911" s="8">
+        <v>30353.0</v>
+      </c>
+      <c r="C911" s="14">
+        <v>30353.0</v>
+      </c>
+      <c r="D911" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E911" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="F911" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G911" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H911" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I911" s="21"/>
-      <c r="J911" s="21"/>
+      <c r="I911" s="11">
+        <v>46277.0</v>
+      </c>
+      <c r="J911" s="11">
+        <v>46277.0</v>
+      </c>
       <c r="K911" s="10" t="s">
         <v>20</v>
       </c>
@@ -43342,17 +44645,33 @@
     </row>
     <row r="912" ht="18.0" customHeight="1">
       <c r="A912" s="6"/>
-      <c r="B912" s="17"/>
-      <c r="C912" s="14"/>
-      <c r="D912" s="20"/>
-      <c r="E912" s="15"/>
-      <c r="F912" s="15"/>
-      <c r="G912" s="15"/>
+      <c r="B912" s="8">
+        <v>32348.0</v>
+      </c>
+      <c r="C912" s="14">
+        <v>32348.0</v>
+      </c>
+      <c r="D912" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E912" s="16" t="s">
+        <v>839</v>
+      </c>
+      <c r="F912" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G912" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H912" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I912" s="21"/>
-      <c r="J912" s="21"/>
+      <c r="I912" s="11">
+        <v>46295.0</v>
+      </c>
+      <c r="J912" s="11">
+        <v>46295.0</v>
+      </c>
       <c r="K912" s="10" t="s">
         <v>20</v>
       </c>
@@ -43368,17 +44687,33 @@
     </row>
     <row r="913" ht="18.0" customHeight="1">
       <c r="A913" s="6"/>
-      <c r="B913" s="17"/>
-      <c r="C913" s="14"/>
-      <c r="D913" s="20"/>
-      <c r="E913" s="15"/>
-      <c r="F913" s="15"/>
-      <c r="G913" s="15"/>
+      <c r="B913" s="8">
+        <v>32348.0</v>
+      </c>
+      <c r="C913" s="14">
+        <v>32348.0</v>
+      </c>
+      <c r="D913" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E913" s="16" t="s">
+        <v>839</v>
+      </c>
+      <c r="F913" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G913" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H913" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I913" s="21"/>
-      <c r="J913" s="21"/>
+      <c r="I913" s="11">
+        <v>46296.0</v>
+      </c>
+      <c r="J913" s="11">
+        <v>46296.0</v>
+      </c>
       <c r="K913" s="10" t="s">
         <v>20</v>
       </c>
@@ -43394,17 +44729,33 @@
     </row>
     <row r="914" ht="18.0" customHeight="1">
       <c r="A914" s="6"/>
-      <c r="B914" s="17"/>
-      <c r="C914" s="14"/>
-      <c r="D914" s="20"/>
-      <c r="E914" s="15"/>
-      <c r="F914" s="15"/>
-      <c r="G914" s="15"/>
+      <c r="B914" s="8">
+        <v>31962.0</v>
+      </c>
+      <c r="C914" s="14">
+        <v>31962.0</v>
+      </c>
+      <c r="D914" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E914" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="F914" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G914" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H914" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I914" s="21"/>
-      <c r="J914" s="21"/>
+      <c r="I914" s="11">
+        <v>46285.0</v>
+      </c>
+      <c r="J914" s="11">
+        <v>46285.0</v>
+      </c>
       <c r="K914" s="10" t="s">
         <v>20</v>
       </c>
@@ -43420,17 +44771,33 @@
     </row>
     <row r="915" ht="18.0" customHeight="1">
       <c r="A915" s="6"/>
-      <c r="B915" s="17"/>
-      <c r="C915" s="14"/>
-      <c r="D915" s="20"/>
-      <c r="E915" s="15"/>
-      <c r="F915" s="15"/>
-      <c r="G915" s="15"/>
+      <c r="B915" s="8">
+        <v>31962.0</v>
+      </c>
+      <c r="C915" s="14">
+        <v>31962.0</v>
+      </c>
+      <c r="D915" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E915" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="F915" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G915" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H915" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I915" s="21"/>
-      <c r="J915" s="21"/>
+      <c r="I915" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J915" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K915" s="10" t="s">
         <v>20</v>
       </c>
@@ -43446,17 +44813,33 @@
     </row>
     <row r="916" ht="18.0" customHeight="1">
       <c r="A916" s="6"/>
-      <c r="B916" s="17"/>
-      <c r="C916" s="14"/>
-      <c r="D916" s="20"/>
-      <c r="E916" s="15"/>
-      <c r="F916" s="15"/>
-      <c r="G916" s="15"/>
+      <c r="B916" s="8">
+        <v>31962.0</v>
+      </c>
+      <c r="C916" s="14">
+        <v>31962.0</v>
+      </c>
+      <c r="D916" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E916" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="F916" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G916" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H916" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I916" s="21"/>
-      <c r="J916" s="21"/>
+      <c r="I916" s="11">
+        <v>46291.0</v>
+      </c>
+      <c r="J916" s="11">
+        <v>46291.0</v>
+      </c>
       <c r="K916" s="10" t="s">
         <v>20</v>
       </c>
@@ -43472,17 +44855,33 @@
     </row>
     <row r="917" ht="18.0" customHeight="1">
       <c r="A917" s="6"/>
-      <c r="B917" s="17"/>
-      <c r="C917" s="14"/>
-      <c r="D917" s="20"/>
-      <c r="E917" s="15"/>
-      <c r="F917" s="15"/>
-      <c r="G917" s="15"/>
+      <c r="B917" s="8">
+        <v>30497.0</v>
+      </c>
+      <c r="C917" s="14">
+        <v>30497.0</v>
+      </c>
+      <c r="D917" s="9" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E917" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F917" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G917" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H917" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I917" s="21"/>
-      <c r="J917" s="21"/>
+      <c r="I917" s="11">
+        <v>46294.0</v>
+      </c>
+      <c r="J917" s="11">
+        <v>46294.0</v>
+      </c>
       <c r="K917" s="10" t="s">
         <v>20</v>
       </c>
@@ -43498,17 +44897,33 @@
     </row>
     <row r="918" ht="18.0" customHeight="1">
       <c r="A918" s="6"/>
-      <c r="B918" s="17"/>
-      <c r="C918" s="14"/>
-      <c r="D918" s="20"/>
-      <c r="E918" s="15"/>
-      <c r="F918" s="15"/>
-      <c r="G918" s="15"/>
+      <c r="B918" s="8">
+        <v>30497.0</v>
+      </c>
+      <c r="C918" s="14">
+        <v>30497.0</v>
+      </c>
+      <c r="D918" s="9" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E918" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F918" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G918" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H918" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I918" s="21"/>
-      <c r="J918" s="21"/>
+      <c r="I918" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J918" s="11">
+        <v>46258.0</v>
+      </c>
       <c r="K918" s="10" t="s">
         <v>20</v>
       </c>
@@ -43524,17 +44939,33 @@
     </row>
     <row r="919" ht="18.0" customHeight="1">
       <c r="A919" s="6"/>
-      <c r="B919" s="17"/>
-      <c r="C919" s="14"/>
-      <c r="D919" s="20"/>
-      <c r="E919" s="15"/>
-      <c r="F919" s="15"/>
-      <c r="G919" s="15"/>
+      <c r="B919" s="8">
+        <v>30497.0</v>
+      </c>
+      <c r="C919" s="14">
+        <v>30497.0</v>
+      </c>
+      <c r="D919" s="9" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E919" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F919" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G919" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H919" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I919" s="21"/>
-      <c r="J919" s="21"/>
+      <c r="I919" s="11">
+        <v>46284.0</v>
+      </c>
+      <c r="J919" s="11">
+        <v>46284.0</v>
+      </c>
       <c r="K919" s="10" t="s">
         <v>20</v>
       </c>
@@ -43550,17 +44981,33 @@
     </row>
     <row r="920" ht="18.0" customHeight="1">
       <c r="A920" s="6"/>
-      <c r="B920" s="17"/>
-      <c r="C920" s="14"/>
-      <c r="D920" s="20"/>
-      <c r="E920" s="15"/>
-      <c r="F920" s="15"/>
-      <c r="G920" s="15"/>
+      <c r="B920" s="8">
+        <v>30497.0</v>
+      </c>
+      <c r="C920" s="14">
+        <v>30497.0</v>
+      </c>
+      <c r="D920" s="9" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E920" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F920" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G920" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H920" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I920" s="21"/>
-      <c r="J920" s="21"/>
+      <c r="I920" s="11">
+        <v>46282.0</v>
+      </c>
+      <c r="J920" s="11">
+        <v>46282.0</v>
+      </c>
       <c r="K920" s="10" t="s">
         <v>20</v>
       </c>
@@ -43576,17 +45023,33 @@
     </row>
     <row r="921" ht="18.0" customHeight="1">
       <c r="A921" s="6"/>
-      <c r="B921" s="17"/>
-      <c r="C921" s="14"/>
-      <c r="D921" s="20"/>
-      <c r="E921" s="15"/>
-      <c r="F921" s="15"/>
-      <c r="G921" s="15"/>
+      <c r="B921" s="8">
+        <v>26796.0</v>
+      </c>
+      <c r="C921" s="14">
+        <v>26796.0</v>
+      </c>
+      <c r="D921" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E921" s="16" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F921" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="G921" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H921" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I921" s="21"/>
-      <c r="J921" s="21"/>
+      <c r="I921" s="11">
+        <v>46305.0</v>
+      </c>
+      <c r="J921" s="11">
+        <v>46305.0</v>
+      </c>
       <c r="K921" s="10" t="s">
         <v>20</v>
       </c>
@@ -43602,17 +45065,33 @@
     </row>
     <row r="922" ht="18.0" customHeight="1">
       <c r="A922" s="6"/>
-      <c r="B922" s="17"/>
-      <c r="C922" s="14"/>
-      <c r="D922" s="20"/>
-      <c r="E922" s="15"/>
-      <c r="F922" s="15"/>
-      <c r="G922" s="15"/>
+      <c r="B922" s="8">
+        <v>31456.0</v>
+      </c>
+      <c r="C922" s="14">
+        <v>31456.0</v>
+      </c>
+      <c r="D922" s="9" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E922" s="16" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F922" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G922" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H922" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I922" s="21"/>
-      <c r="J922" s="21"/>
+      <c r="I922" s="11">
+        <v>46299.0</v>
+      </c>
+      <c r="J922" s="11">
+        <v>46300.0</v>
+      </c>
       <c r="K922" s="10" t="s">
         <v>20</v>
       </c>
@@ -43628,17 +45107,33 @@
     </row>
     <row r="923" ht="18.0" customHeight="1">
       <c r="A923" s="6"/>
-      <c r="B923" s="17"/>
-      <c r="C923" s="14"/>
-      <c r="D923" s="20"/>
-      <c r="E923" s="15"/>
-      <c r="F923" s="15"/>
-      <c r="G923" s="15"/>
+      <c r="B923" s="8">
+        <v>27912.0</v>
+      </c>
+      <c r="C923" s="14">
+        <v>27912.0</v>
+      </c>
+      <c r="D923" s="9" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E923" s="16" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F923" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G923" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H923" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I923" s="21"/>
-      <c r="J923" s="21"/>
+      <c r="I923" s="11">
+        <v>46282.0</v>
+      </c>
+      <c r="J923" s="11">
+        <v>46282.0</v>
+      </c>
       <c r="K923" s="10" t="s">
         <v>20</v>
       </c>
@@ -43654,17 +45149,33 @@
     </row>
     <row r="924" ht="18.0" customHeight="1">
       <c r="A924" s="6"/>
-      <c r="B924" s="17"/>
-      <c r="C924" s="14"/>
-      <c r="D924" s="20"/>
-      <c r="E924" s="15"/>
-      <c r="F924" s="15"/>
-      <c r="G924" s="15"/>
+      <c r="B924" s="8">
+        <v>27912.0</v>
+      </c>
+      <c r="C924" s="14">
+        <v>27912.0</v>
+      </c>
+      <c r="D924" s="9" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E924" s="16" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F924" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G924" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H924" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I924" s="21"/>
-      <c r="J924" s="21"/>
+      <c r="I924" s="11">
+        <v>46299.0</v>
+      </c>
+      <c r="J924" s="11">
+        <v>46299.0</v>
+      </c>
       <c r="K924" s="10" t="s">
         <v>20</v>
       </c>
@@ -43680,17 +45191,33 @@
     </row>
     <row r="925" ht="18.0" customHeight="1">
       <c r="A925" s="6"/>
-      <c r="B925" s="17"/>
-      <c r="C925" s="14"/>
-      <c r="D925" s="20"/>
-      <c r="E925" s="15"/>
-      <c r="F925" s="15"/>
-      <c r="G925" s="15"/>
+      <c r="B925" s="8">
+        <v>32031.0</v>
+      </c>
+      <c r="C925" s="14">
+        <v>32031.0</v>
+      </c>
+      <c r="D925" s="9" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E925" s="16" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F925" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G925" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H925" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I925" s="21"/>
-      <c r="J925" s="21"/>
+      <c r="I925" s="11">
+        <v>46289.0</v>
+      </c>
+      <c r="J925" s="11">
+        <v>46289.0</v>
+      </c>
       <c r="K925" s="10" t="s">
         <v>20</v>
       </c>
@@ -43706,17 +45233,33 @@
     </row>
     <row r="926" ht="18.0" customHeight="1">
       <c r="A926" s="6"/>
-      <c r="B926" s="17"/>
-      <c r="C926" s="14"/>
-      <c r="D926" s="20"/>
-      <c r="E926" s="15"/>
-      <c r="F926" s="15"/>
-      <c r="G926" s="15"/>
+      <c r="B926" s="8">
+        <v>17666.0</v>
+      </c>
+      <c r="C926" s="14">
+        <v>17666.0</v>
+      </c>
+      <c r="D926" s="9" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E926" s="16" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F926" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G926" s="18" t="s">
+        <v>1294</v>
+      </c>
       <c r="H926" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I926" s="21"/>
-      <c r="J926" s="21"/>
+      <c r="I926" s="11">
+        <v>46284.0</v>
+      </c>
+      <c r="J926" s="11">
+        <v>46284.0</v>
+      </c>
       <c r="K926" s="10" t="s">
         <v>20</v>
       </c>
@@ -43732,17 +45275,33 @@
     </row>
     <row r="927" ht="18.0" customHeight="1">
       <c r="A927" s="6"/>
-      <c r="B927" s="17"/>
-      <c r="C927" s="14"/>
-      <c r="D927" s="20"/>
-      <c r="E927" s="15"/>
-      <c r="F927" s="15"/>
-      <c r="G927" s="15"/>
+      <c r="B927" s="8">
+        <v>26226.0</v>
+      </c>
+      <c r="C927" s="14">
+        <v>26226.0</v>
+      </c>
+      <c r="D927" s="9" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E927" s="16" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F927" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="G927" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H927" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I927" s="21"/>
-      <c r="J927" s="21"/>
+      <c r="I927" s="11">
+        <v>46292.0</v>
+      </c>
+      <c r="J927" s="11">
+        <v>46292.0</v>
+      </c>
       <c r="K927" s="10" t="s">
         <v>20</v>
       </c>
@@ -43758,17 +45317,29 @@
     </row>
     <row r="928" ht="18.0" customHeight="1">
       <c r="A928" s="6"/>
-      <c r="B928" s="17"/>
-      <c r="C928" s="14"/>
-      <c r="D928" s="20"/>
-      <c r="E928" s="15"/>
-      <c r="F928" s="15"/>
-      <c r="G928" s="15"/>
+      <c r="B928" s="8">
+        <v>31442.0</v>
+      </c>
+      <c r="C928" s="14">
+        <v>31442.0</v>
+      </c>
+      <c r="D928" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E928" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F928" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G928" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H928" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I928" s="21"/>
-      <c r="J928" s="21"/>
+      <c r="I928" s="20"/>
+      <c r="J928" s="20"/>
       <c r="K928" s="10" t="s">
         <v>20</v>
       </c>
@@ -43784,17 +45355,29 @@
     </row>
     <row r="929" ht="18.0" customHeight="1">
       <c r="A929" s="6"/>
-      <c r="B929" s="17"/>
-      <c r="C929" s="14"/>
-      <c r="D929" s="20"/>
-      <c r="E929" s="15"/>
-      <c r="F929" s="15"/>
-      <c r="G929" s="15"/>
+      <c r="B929" s="8">
+        <v>31442.0</v>
+      </c>
+      <c r="C929" s="14">
+        <v>31442.0</v>
+      </c>
+      <c r="D929" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E929" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F929" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G929" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H929" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I929" s="21"/>
-      <c r="J929" s="21"/>
+      <c r="I929" s="20"/>
+      <c r="J929" s="20"/>
       <c r="K929" s="10" t="s">
         <v>20</v>
       </c>
@@ -43810,17 +45393,29 @@
     </row>
     <row r="930" ht="18.0" customHeight="1">
       <c r="A930" s="6"/>
-      <c r="B930" s="17"/>
-      <c r="C930" s="14"/>
-      <c r="D930" s="20"/>
-      <c r="E930" s="15"/>
-      <c r="F930" s="15"/>
-      <c r="G930" s="15"/>
+      <c r="B930" s="8">
+        <v>31442.0</v>
+      </c>
+      <c r="C930" s="14">
+        <v>31442.0</v>
+      </c>
+      <c r="D930" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E930" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F930" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G930" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H930" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I930" s="21"/>
-      <c r="J930" s="21"/>
+      <c r="I930" s="20"/>
+      <c r="J930" s="20"/>
       <c r="K930" s="10" t="s">
         <v>20</v>
       </c>
@@ -43836,17 +45431,29 @@
     </row>
     <row r="931" ht="18.0" customHeight="1">
       <c r="A931" s="6"/>
-      <c r="B931" s="17"/>
-      <c r="C931" s="14"/>
-      <c r="D931" s="20"/>
-      <c r="E931" s="15"/>
-      <c r="F931" s="15"/>
-      <c r="G931" s="15"/>
+      <c r="B931" s="8">
+        <v>31442.0</v>
+      </c>
+      <c r="C931" s="14">
+        <v>31442.0</v>
+      </c>
+      <c r="D931" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E931" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F931" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G931" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H931" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I931" s="21"/>
-      <c r="J931" s="21"/>
+      <c r="I931" s="20"/>
+      <c r="J931" s="20"/>
       <c r="K931" s="10" t="s">
         <v>20</v>
       </c>
@@ -43864,15 +45471,15 @@
       <c r="A932" s="6"/>
       <c r="B932" s="17"/>
       <c r="C932" s="14"/>
-      <c r="D932" s="20"/>
+      <c r="D932" s="22"/>
       <c r="E932" s="15"/>
       <c r="F932" s="15"/>
       <c r="G932" s="15"/>
       <c r="H932" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I932" s="21"/>
-      <c r="J932" s="21"/>
+      <c r="I932" s="20"/>
+      <c r="J932" s="20"/>
       <c r="K932" s="10" t="s">
         <v>20</v>
       </c>
@@ -43890,15 +45497,15 @@
       <c r="A933" s="6"/>
       <c r="B933" s="17"/>
       <c r="C933" s="14"/>
-      <c r="D933" s="20"/>
+      <c r="D933" s="22"/>
       <c r="E933" s="15"/>
       <c r="F933" s="15"/>
       <c r="G933" s="15"/>
       <c r="H933" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I933" s="21"/>
-      <c r="J933" s="21"/>
+      <c r="I933" s="20"/>
+      <c r="J933" s="20"/>
       <c r="K933" s="10" t="s">
         <v>20</v>
       </c>
@@ -43916,15 +45523,15 @@
       <c r="A934" s="6"/>
       <c r="B934" s="17"/>
       <c r="C934" s="14"/>
-      <c r="D934" s="20"/>
+      <c r="D934" s="22"/>
       <c r="E934" s="15"/>
       <c r="F934" s="15"/>
       <c r="G934" s="15"/>
       <c r="H934" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I934" s="21"/>
-      <c r="J934" s="21"/>
+      <c r="I934" s="20"/>
+      <c r="J934" s="20"/>
       <c r="K934" s="10" t="s">
         <v>20</v>
       </c>
@@ -43942,15 +45549,15 @@
       <c r="A935" s="6"/>
       <c r="B935" s="17"/>
       <c r="C935" s="14"/>
-      <c r="D935" s="20"/>
+      <c r="D935" s="22"/>
       <c r="E935" s="15"/>
       <c r="F935" s="15"/>
       <c r="G935" s="15"/>
       <c r="H935" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I935" s="21"/>
-      <c r="J935" s="21"/>
+      <c r="I935" s="20"/>
+      <c r="J935" s="20"/>
       <c r="K935" s="10" t="s">
         <v>20</v>
       </c>
@@ -43968,15 +45575,15 @@
       <c r="A936" s="6"/>
       <c r="B936" s="17"/>
       <c r="C936" s="14"/>
-      <c r="D936" s="20"/>
+      <c r="D936" s="22"/>
       <c r="E936" s="15"/>
       <c r="F936" s="15"/>
       <c r="G936" s="15"/>
       <c r="H936" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I936" s="21"/>
-      <c r="J936" s="21"/>
+      <c r="I936" s="20"/>
+      <c r="J936" s="20"/>
       <c r="K936" s="10" t="s">
         <v>20</v>
       </c>
@@ -43994,15 +45601,15 @@
       <c r="A937" s="6"/>
       <c r="B937" s="17"/>
       <c r="C937" s="14"/>
-      <c r="D937" s="20"/>
+      <c r="D937" s="22"/>
       <c r="E937" s="15"/>
       <c r="F937" s="15"/>
       <c r="G937" s="15"/>
       <c r="H937" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I937" s="21"/>
-      <c r="J937" s="21"/>
+      <c r="I937" s="20"/>
+      <c r="J937" s="20"/>
       <c r="K937" s="10" t="s">
         <v>20</v>
       </c>
@@ -44020,15 +45627,15 @@
       <c r="A938" s="6"/>
       <c r="B938" s="17"/>
       <c r="C938" s="14"/>
-      <c r="D938" s="20"/>
+      <c r="D938" s="22"/>
       <c r="E938" s="15"/>
       <c r="F938" s="15"/>
       <c r="G938" s="15"/>
       <c r="H938" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I938" s="21"/>
-      <c r="J938" s="21"/>
+      <c r="I938" s="20"/>
+      <c r="J938" s="20"/>
       <c r="K938" s="10" t="s">
         <v>20</v>
       </c>
@@ -44046,15 +45653,15 @@
       <c r="A939" s="6"/>
       <c r="B939" s="17"/>
       <c r="C939" s="14"/>
-      <c r="D939" s="20"/>
+      <c r="D939" s="22"/>
       <c r="E939" s="15"/>
       <c r="F939" s="15"/>
       <c r="G939" s="15"/>
       <c r="H939" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I939" s="21"/>
-      <c r="J939" s="21"/>
+      <c r="I939" s="20"/>
+      <c r="J939" s="20"/>
       <c r="K939" s="10" t="s">
         <v>20</v>
       </c>
@@ -44072,15 +45679,15 @@
       <c r="A940" s="6"/>
       <c r="B940" s="17"/>
       <c r="C940" s="14"/>
-      <c r="D940" s="20"/>
+      <c r="D940" s="22"/>
       <c r="E940" s="15"/>
       <c r="F940" s="15"/>
       <c r="G940" s="15"/>
       <c r="H940" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I940" s="21"/>
-      <c r="J940" s="21"/>
+      <c r="I940" s="20"/>
+      <c r="J940" s="20"/>
       <c r="K940" s="10" t="s">
         <v>20</v>
       </c>
@@ -44098,15 +45705,15 @@
       <c r="A941" s="6"/>
       <c r="B941" s="17"/>
       <c r="C941" s="14"/>
-      <c r="D941" s="20"/>
+      <c r="D941" s="22"/>
       <c r="E941" s="15"/>
       <c r="F941" s="15"/>
       <c r="G941" s="15"/>
       <c r="H941" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I941" s="21"/>
-      <c r="J941" s="21"/>
+      <c r="I941" s="20"/>
+      <c r="J941" s="20"/>
       <c r="K941" s="10" t="s">
         <v>20</v>
       </c>
@@ -44124,15 +45731,15 @@
       <c r="A942" s="6"/>
       <c r="B942" s="17"/>
       <c r="C942" s="14"/>
-      <c r="D942" s="20"/>
+      <c r="D942" s="22"/>
       <c r="E942" s="15"/>
       <c r="F942" s="15"/>
       <c r="G942" s="15"/>
       <c r="H942" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I942" s="21"/>
-      <c r="J942" s="21"/>
+      <c r="I942" s="20"/>
+      <c r="J942" s="20"/>
       <c r="K942" s="10" t="s">
         <v>20</v>
       </c>
@@ -44150,15 +45757,15 @@
       <c r="A943" s="6"/>
       <c r="B943" s="17"/>
       <c r="C943" s="14"/>
-      <c r="D943" s="20"/>
+      <c r="D943" s="22"/>
       <c r="E943" s="15"/>
       <c r="F943" s="15"/>
       <c r="G943" s="15"/>
       <c r="H943" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I943" s="21"/>
-      <c r="J943" s="21"/>
+      <c r="I943" s="20"/>
+      <c r="J943" s="20"/>
       <c r="K943" s="10" t="s">
         <v>20</v>
       </c>
@@ -44176,15 +45783,15 @@
       <c r="A944" s="6"/>
       <c r="B944" s="17"/>
       <c r="C944" s="14"/>
-      <c r="D944" s="20"/>
+      <c r="D944" s="22"/>
       <c r="E944" s="15"/>
       <c r="F944" s="15"/>
       <c r="G944" s="15"/>
       <c r="H944" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I944" s="21"/>
-      <c r="J944" s="21"/>
+      <c r="I944" s="20"/>
+      <c r="J944" s="20"/>
       <c r="K944" s="10" t="s">
         <v>20</v>
       </c>
@@ -44202,15 +45809,15 @@
       <c r="A945" s="6"/>
       <c r="B945" s="17"/>
       <c r="C945" s="14"/>
-      <c r="D945" s="20"/>
+      <c r="D945" s="22"/>
       <c r="E945" s="15"/>
       <c r="F945" s="15"/>
       <c r="G945" s="15"/>
       <c r="H945" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I945" s="21"/>
-      <c r="J945" s="21"/>
+      <c r="I945" s="20"/>
+      <c r="J945" s="20"/>
       <c r="K945" s="10" t="s">
         <v>20</v>
       </c>
@@ -44228,15 +45835,15 @@
       <c r="A946" s="6"/>
       <c r="B946" s="17"/>
       <c r="C946" s="14"/>
-      <c r="D946" s="20"/>
+      <c r="D946" s="22"/>
       <c r="E946" s="15"/>
       <c r="F946" s="15"/>
       <c r="G946" s="15"/>
       <c r="H946" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I946" s="21"/>
-      <c r="J946" s="21"/>
+      <c r="I946" s="20"/>
+      <c r="J946" s="20"/>
       <c r="K946" s="10" t="s">
         <v>20</v>
       </c>
@@ -44254,15 +45861,15 @@
       <c r="A947" s="6"/>
       <c r="B947" s="17"/>
       <c r="C947" s="14"/>
-      <c r="D947" s="20"/>
+      <c r="D947" s="22"/>
       <c r="E947" s="15"/>
       <c r="F947" s="15"/>
       <c r="G947" s="15"/>
       <c r="H947" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I947" s="21"/>
-      <c r="J947" s="21"/>
+      <c r="I947" s="20"/>
+      <c r="J947" s="20"/>
       <c r="K947" s="10" t="s">
         <v>20</v>
       </c>
@@ -44280,15 +45887,15 @@
       <c r="A948" s="6"/>
       <c r="B948" s="17"/>
       <c r="C948" s="14"/>
-      <c r="D948" s="20"/>
+      <c r="D948" s="22"/>
       <c r="E948" s="15"/>
       <c r="F948" s="15"/>
       <c r="G948" s="15"/>
       <c r="H948" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I948" s="21"/>
-      <c r="J948" s="21"/>
+      <c r="I948" s="20"/>
+      <c r="J948" s="20"/>
       <c r="K948" s="10" t="s">
         <v>20</v>
       </c>
@@ -44306,15 +45913,15 @@
       <c r="A949" s="6"/>
       <c r="B949" s="17"/>
       <c r="C949" s="14"/>
-      <c r="D949" s="20"/>
+      <c r="D949" s="22"/>
       <c r="E949" s="15"/>
       <c r="F949" s="15"/>
       <c r="G949" s="15"/>
       <c r="H949" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I949" s="21"/>
-      <c r="J949" s="21"/>
+      <c r="I949" s="20"/>
+      <c r="J949" s="20"/>
       <c r="K949" s="10" t="s">
         <v>20</v>
       </c>
@@ -44332,15 +45939,15 @@
       <c r="A950" s="6"/>
       <c r="B950" s="17"/>
       <c r="C950" s="14"/>
-      <c r="D950" s="20"/>
+      <c r="D950" s="22"/>
       <c r="E950" s="15"/>
       <c r="F950" s="15"/>
       <c r="G950" s="15"/>
       <c r="H950" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I950" s="21"/>
-      <c r="J950" s="21"/>
+      <c r="I950" s="20"/>
+      <c r="J950" s="20"/>
       <c r="K950" s="10" t="s">
         <v>20</v>
       </c>
@@ -44358,15 +45965,15 @@
       <c r="A951" s="6"/>
       <c r="B951" s="17"/>
       <c r="C951" s="14"/>
-      <c r="D951" s="20"/>
+      <c r="D951" s="22"/>
       <c r="E951" s="15"/>
       <c r="F951" s="15"/>
       <c r="G951" s="15"/>
       <c r="H951" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I951" s="21"/>
-      <c r="J951" s="21"/>
+      <c r="I951" s="20"/>
+      <c r="J951" s="20"/>
       <c r="K951" s="10" t="s">
         <v>20</v>
       </c>
@@ -44384,15 +45991,15 @@
       <c r="A952" s="6"/>
       <c r="B952" s="17"/>
       <c r="C952" s="14"/>
-      <c r="D952" s="20"/>
+      <c r="D952" s="22"/>
       <c r="E952" s="15"/>
       <c r="F952" s="15"/>
       <c r="G952" s="15"/>
       <c r="H952" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I952" s="21"/>
-      <c r="J952" s="21"/>
+      <c r="I952" s="20"/>
+      <c r="J952" s="20"/>
       <c r="K952" s="10" t="s">
         <v>20</v>
       </c>
@@ -44410,15 +46017,15 @@
       <c r="A953" s="6"/>
       <c r="B953" s="17"/>
       <c r="C953" s="14"/>
-      <c r="D953" s="20"/>
+      <c r="D953" s="22"/>
       <c r="E953" s="15"/>
       <c r="F953" s="15"/>
       <c r="G953" s="15"/>
       <c r="H953" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I953" s="21"/>
-      <c r="J953" s="21"/>
+      <c r="I953" s="20"/>
+      <c r="J953" s="20"/>
       <c r="K953" s="10" t="s">
         <v>20</v>
       </c>
@@ -44436,15 +46043,15 @@
       <c r="A954" s="6"/>
       <c r="B954" s="17"/>
       <c r="C954" s="14"/>
-      <c r="D954" s="20"/>
+      <c r="D954" s="22"/>
       <c r="E954" s="15"/>
       <c r="F954" s="15"/>
       <c r="G954" s="15"/>
       <c r="H954" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I954" s="21"/>
-      <c r="J954" s="21"/>
+      <c r="I954" s="20"/>
+      <c r="J954" s="20"/>
       <c r="K954" s="10" t="s">
         <v>20</v>
       </c>
@@ -44462,15 +46069,15 @@
       <c r="A955" s="6"/>
       <c r="B955" s="17"/>
       <c r="C955" s="14"/>
-      <c r="D955" s="20"/>
+      <c r="D955" s="22"/>
       <c r="E955" s="15"/>
       <c r="F955" s="15"/>
       <c r="G955" s="15"/>
       <c r="H955" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I955" s="21"/>
-      <c r="J955" s="21"/>
+      <c r="I955" s="20"/>
+      <c r="J955" s="20"/>
       <c r="K955" s="10" t="s">
         <v>20</v>
       </c>
@@ -44488,15 +46095,15 @@
       <c r="A956" s="6"/>
       <c r="B956" s="17"/>
       <c r="C956" s="14"/>
-      <c r="D956" s="20"/>
+      <c r="D956" s="22"/>
       <c r="E956" s="15"/>
       <c r="F956" s="15"/>
       <c r="G956" s="15"/>
       <c r="H956" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I956" s="21"/>
-      <c r="J956" s="21"/>
+      <c r="I956" s="20"/>
+      <c r="J956" s="20"/>
       <c r="K956" s="10" t="s">
         <v>20</v>
       </c>
@@ -44514,15 +46121,15 @@
       <c r="A957" s="6"/>
       <c r="B957" s="17"/>
       <c r="C957" s="14"/>
-      <c r="D957" s="20"/>
+      <c r="D957" s="22"/>
       <c r="E957" s="15"/>
       <c r="F957" s="15"/>
       <c r="G957" s="15"/>
       <c r="H957" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I957" s="21"/>
-      <c r="J957" s="21"/>
+      <c r="I957" s="20"/>
+      <c r="J957" s="20"/>
       <c r="K957" s="10" t="s">
         <v>20</v>
       </c>
@@ -44540,15 +46147,15 @@
       <c r="A958" s="6"/>
       <c r="B958" s="17"/>
       <c r="C958" s="14"/>
-      <c r="D958" s="20"/>
+      <c r="D958" s="22"/>
       <c r="E958" s="15"/>
       <c r="F958" s="15"/>
       <c r="G958" s="15"/>
       <c r="H958" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I958" s="21"/>
-      <c r="J958" s="21"/>
+      <c r="I958" s="20"/>
+      <c r="J958" s="20"/>
       <c r="K958" s="10" t="s">
         <v>20</v>
       </c>
@@ -44566,15 +46173,15 @@
       <c r="A959" s="6"/>
       <c r="B959" s="17"/>
       <c r="C959" s="14"/>
-      <c r="D959" s="20"/>
+      <c r="D959" s="22"/>
       <c r="E959" s="15"/>
       <c r="F959" s="15"/>
       <c r="G959" s="15"/>
       <c r="H959" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I959" s="21"/>
-      <c r="J959" s="21"/>
+      <c r="I959" s="20"/>
+      <c r="J959" s="20"/>
       <c r="K959" s="10" t="s">
         <v>20</v>
       </c>
@@ -44592,15 +46199,15 @@
       <c r="A960" s="6"/>
       <c r="B960" s="17"/>
       <c r="C960" s="14"/>
-      <c r="D960" s="20"/>
+      <c r="D960" s="22"/>
       <c r="E960" s="15"/>
       <c r="F960" s="15"/>
       <c r="G960" s="15"/>
       <c r="H960" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I960" s="21"/>
-      <c r="J960" s="21"/>
+      <c r="I960" s="20"/>
+      <c r="J960" s="20"/>
       <c r="K960" s="10" t="s">
         <v>20</v>
       </c>
@@ -44618,15 +46225,15 @@
       <c r="A961" s="6"/>
       <c r="B961" s="17"/>
       <c r="C961" s="14"/>
-      <c r="D961" s="20"/>
+      <c r="D961" s="22"/>
       <c r="E961" s="15"/>
       <c r="F961" s="15"/>
       <c r="G961" s="15"/>
       <c r="H961" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I961" s="21"/>
-      <c r="J961" s="21"/>
+      <c r="I961" s="20"/>
+      <c r="J961" s="20"/>
       <c r="K961" s="10" t="s">
         <v>20</v>
       </c>
@@ -44644,15 +46251,15 @@
       <c r="A962" s="6"/>
       <c r="B962" s="17"/>
       <c r="C962" s="14"/>
-      <c r="D962" s="20"/>
+      <c r="D962" s="22"/>
       <c r="E962" s="15"/>
       <c r="F962" s="15"/>
       <c r="G962" s="15"/>
       <c r="H962" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I962" s="21"/>
-      <c r="J962" s="21"/>
+      <c r="I962" s="20"/>
+      <c r="J962" s="20"/>
       <c r="K962" s="10" t="s">
         <v>20</v>
       </c>
@@ -44670,15 +46277,15 @@
       <c r="A963" s="6"/>
       <c r="B963" s="17"/>
       <c r="C963" s="14"/>
-      <c r="D963" s="20"/>
+      <c r="D963" s="22"/>
       <c r="E963" s="15"/>
       <c r="F963" s="15"/>
       <c r="G963" s="15"/>
       <c r="H963" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I963" s="21"/>
-      <c r="J963" s="21"/>
+      <c r="I963" s="20"/>
+      <c r="J963" s="20"/>
       <c r="K963" s="10" t="s">
         <v>20</v>
       </c>
@@ -44696,15 +46303,15 @@
       <c r="A964" s="6"/>
       <c r="B964" s="17"/>
       <c r="C964" s="14"/>
-      <c r="D964" s="20"/>
+      <c r="D964" s="22"/>
       <c r="E964" s="15"/>
       <c r="F964" s="15"/>
       <c r="G964" s="15"/>
       <c r="H964" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I964" s="21"/>
-      <c r="J964" s="21"/>
+      <c r="I964" s="20"/>
+      <c r="J964" s="20"/>
       <c r="K964" s="10" t="s">
         <v>20</v>
       </c>
@@ -44722,15 +46329,15 @@
       <c r="A965" s="6"/>
       <c r="B965" s="17"/>
       <c r="C965" s="14"/>
-      <c r="D965" s="20"/>
+      <c r="D965" s="22"/>
       <c r="E965" s="15"/>
       <c r="F965" s="15"/>
       <c r="G965" s="15"/>
       <c r="H965" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I965" s="21"/>
-      <c r="J965" s="21"/>
+      <c r="I965" s="20"/>
+      <c r="J965" s="20"/>
       <c r="K965" s="10" t="s">
         <v>20</v>
       </c>
@@ -44748,15 +46355,15 @@
       <c r="A966" s="6"/>
       <c r="B966" s="17"/>
       <c r="C966" s="14"/>
-      <c r="D966" s="20"/>
+      <c r="D966" s="22"/>
       <c r="E966" s="15"/>
       <c r="F966" s="15"/>
       <c r="G966" s="15"/>
       <c r="H966" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I966" s="21"/>
-      <c r="J966" s="21"/>
+      <c r="I966" s="20"/>
+      <c r="J966" s="20"/>
       <c r="K966" s="10" t="s">
         <v>20</v>
       </c>
@@ -44774,15 +46381,15 @@
       <c r="A967" s="6"/>
       <c r="B967" s="17"/>
       <c r="C967" s="14"/>
-      <c r="D967" s="20"/>
+      <c r="D967" s="22"/>
       <c r="E967" s="15"/>
       <c r="F967" s="15"/>
       <c r="G967" s="15"/>
       <c r="H967" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I967" s="21"/>
-      <c r="J967" s="21"/>
+      <c r="I967" s="20"/>
+      <c r="J967" s="20"/>
       <c r="K967" s="10" t="s">
         <v>20</v>
       </c>
@@ -44800,15 +46407,15 @@
       <c r="A968" s="6"/>
       <c r="B968" s="17"/>
       <c r="C968" s="14"/>
-      <c r="D968" s="20"/>
+      <c r="D968" s="22"/>
       <c r="E968" s="15"/>
       <c r="F968" s="15"/>
       <c r="G968" s="15"/>
       <c r="H968" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I968" s="21"/>
-      <c r="J968" s="21"/>
+      <c r="I968" s="20"/>
+      <c r="J968" s="20"/>
       <c r="K968" s="10" t="s">
         <v>20</v>
       </c>
@@ -44826,15 +46433,15 @@
       <c r="A969" s="6"/>
       <c r="B969" s="17"/>
       <c r="C969" s="14"/>
-      <c r="D969" s="20"/>
+      <c r="D969" s="22"/>
       <c r="E969" s="15"/>
       <c r="F969" s="15"/>
       <c r="G969" s="15"/>
       <c r="H969" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I969" s="21"/>
-      <c r="J969" s="21"/>
+      <c r="I969" s="20"/>
+      <c r="J969" s="20"/>
       <c r="K969" s="10" t="s">
         <v>20</v>
       </c>
@@ -44852,15 +46459,15 @@
       <c r="A970" s="6"/>
       <c r="B970" s="17"/>
       <c r="C970" s="14"/>
-      <c r="D970" s="20"/>
+      <c r="D970" s="22"/>
       <c r="E970" s="15"/>
       <c r="F970" s="15"/>
       <c r="G970" s="15"/>
       <c r="H970" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I970" s="21"/>
-      <c r="J970" s="21"/>
+      <c r="I970" s="20"/>
+      <c r="J970" s="20"/>
       <c r="K970" s="10" t="s">
         <v>20</v>
       </c>
@@ -44878,15 +46485,15 @@
       <c r="A971" s="6"/>
       <c r="B971" s="17"/>
       <c r="C971" s="14"/>
-      <c r="D971" s="20"/>
+      <c r="D971" s="22"/>
       <c r="E971" s="15"/>
       <c r="F971" s="15"/>
       <c r="G971" s="15"/>
       <c r="H971" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I971" s="21"/>
-      <c r="J971" s="21"/>
+      <c r="I971" s="20"/>
+      <c r="J971" s="20"/>
       <c r="K971" s="10" t="s">
         <v>20</v>
       </c>
@@ -44904,15 +46511,15 @@
       <c r="A972" s="6"/>
       <c r="B972" s="17"/>
       <c r="C972" s="14"/>
-      <c r="D972" s="20"/>
+      <c r="D972" s="22"/>
       <c r="E972" s="15"/>
       <c r="F972" s="15"/>
       <c r="G972" s="15"/>
       <c r="H972" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I972" s="21"/>
-      <c r="J972" s="21"/>
+      <c r="I972" s="20"/>
+      <c r="J972" s="20"/>
       <c r="K972" s="10" t="s">
         <v>20</v>
       </c>
@@ -44930,15 +46537,15 @@
       <c r="A973" s="6"/>
       <c r="B973" s="17"/>
       <c r="C973" s="14"/>
-      <c r="D973" s="20"/>
+      <c r="D973" s="22"/>
       <c r="E973" s="15"/>
       <c r="F973" s="15"/>
       <c r="G973" s="15"/>
       <c r="H973" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I973" s="21"/>
-      <c r="J973" s="21"/>
+      <c r="I973" s="20"/>
+      <c r="J973" s="20"/>
       <c r="K973" s="10" t="s">
         <v>20</v>
       </c>
@@ -44956,15 +46563,15 @@
       <c r="A974" s="6"/>
       <c r="B974" s="17"/>
       <c r="C974" s="14"/>
-      <c r="D974" s="20"/>
+      <c r="D974" s="22"/>
       <c r="E974" s="15"/>
       <c r="F974" s="15"/>
       <c r="G974" s="15"/>
       <c r="H974" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I974" s="21"/>
-      <c r="J974" s="21"/>
+      <c r="I974" s="20"/>
+      <c r="J974" s="20"/>
       <c r="K974" s="10" t="s">
         <v>20</v>
       </c>
@@ -44982,15 +46589,15 @@
       <c r="A975" s="6"/>
       <c r="B975" s="17"/>
       <c r="C975" s="14"/>
-      <c r="D975" s="20"/>
+      <c r="D975" s="22"/>
       <c r="E975" s="15"/>
       <c r="F975" s="15"/>
       <c r="G975" s="15"/>
       <c r="H975" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I975" s="21"/>
-      <c r="J975" s="21"/>
+      <c r="I975" s="20"/>
+      <c r="J975" s="20"/>
       <c r="K975" s="10" t="s">
         <v>20</v>
       </c>
@@ -45008,15 +46615,15 @@
       <c r="A976" s="6"/>
       <c r="B976" s="17"/>
       <c r="C976" s="14"/>
-      <c r="D976" s="20"/>
+      <c r="D976" s="22"/>
       <c r="E976" s="15"/>
       <c r="F976" s="15"/>
       <c r="G976" s="15"/>
       <c r="H976" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I976" s="21"/>
-      <c r="J976" s="21"/>
+      <c r="I976" s="20"/>
+      <c r="J976" s="20"/>
       <c r="K976" s="10" t="s">
         <v>20</v>
       </c>
@@ -45034,15 +46641,15 @@
       <c r="A977" s="6"/>
       <c r="B977" s="17"/>
       <c r="C977" s="14"/>
-      <c r="D977" s="20"/>
+      <c r="D977" s="22"/>
       <c r="E977" s="15"/>
       <c r="F977" s="15"/>
       <c r="G977" s="15"/>
       <c r="H977" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I977" s="21"/>
-      <c r="J977" s="21"/>
+      <c r="I977" s="20"/>
+      <c r="J977" s="20"/>
       <c r="K977" s="10" t="s">
         <v>20</v>
       </c>
@@ -45060,15 +46667,15 @@
       <c r="A978" s="6"/>
       <c r="B978" s="17"/>
       <c r="C978" s="14"/>
-      <c r="D978" s="20"/>
+      <c r="D978" s="22"/>
       <c r="E978" s="15"/>
       <c r="F978" s="15"/>
       <c r="G978" s="15"/>
       <c r="H978" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I978" s="21"/>
-      <c r="J978" s="21"/>
+      <c r="I978" s="20"/>
+      <c r="J978" s="20"/>
       <c r="K978" s="10" t="s">
         <v>20</v>
       </c>
@@ -45086,15 +46693,15 @@
       <c r="A979" s="6"/>
       <c r="B979" s="17"/>
       <c r="C979" s="14"/>
-      <c r="D979" s="20"/>
+      <c r="D979" s="22"/>
       <c r="E979" s="15"/>
       <c r="F979" s="15"/>
       <c r="G979" s="15"/>
       <c r="H979" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I979" s="21"/>
-      <c r="J979" s="21"/>
+      <c r="I979" s="20"/>
+      <c r="J979" s="20"/>
       <c r="K979" s="10" t="s">
         <v>20</v>
       </c>
@@ -45112,15 +46719,15 @@
       <c r="A980" s="6"/>
       <c r="B980" s="17"/>
       <c r="C980" s="14"/>
-      <c r="D980" s="20"/>
+      <c r="D980" s="22"/>
       <c r="E980" s="15"/>
       <c r="F980" s="15"/>
       <c r="G980" s="15"/>
       <c r="H980" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I980" s="21"/>
-      <c r="J980" s="21"/>
+      <c r="I980" s="20"/>
+      <c r="J980" s="20"/>
       <c r="K980" s="10" t="s">
         <v>20</v>
       </c>
@@ -45138,15 +46745,15 @@
       <c r="A981" s="6"/>
       <c r="B981" s="17"/>
       <c r="C981" s="14"/>
-      <c r="D981" s="20"/>
+      <c r="D981" s="22"/>
       <c r="E981" s="15"/>
       <c r="F981" s="15"/>
       <c r="G981" s="15"/>
       <c r="H981" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I981" s="21"/>
-      <c r="J981" s="21"/>
+      <c r="I981" s="20"/>
+      <c r="J981" s="20"/>
       <c r="K981" s="10" t="s">
         <v>20</v>
       </c>
@@ -45164,15 +46771,15 @@
       <c r="A982" s="6"/>
       <c r="B982" s="17"/>
       <c r="C982" s="14"/>
-      <c r="D982" s="20"/>
+      <c r="D982" s="22"/>
       <c r="E982" s="15"/>
       <c r="F982" s="15"/>
       <c r="G982" s="15"/>
       <c r="H982" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I982" s="21"/>
-      <c r="J982" s="21"/>
+      <c r="I982" s="20"/>
+      <c r="J982" s="20"/>
       <c r="K982" s="10" t="s">
         <v>20</v>
       </c>
@@ -45190,15 +46797,15 @@
       <c r="A983" s="6"/>
       <c r="B983" s="17"/>
       <c r="C983" s="14"/>
-      <c r="D983" s="20"/>
+      <c r="D983" s="22"/>
       <c r="E983" s="15"/>
       <c r="F983" s="15"/>
       <c r="G983" s="15"/>
       <c r="H983" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I983" s="21"/>
-      <c r="J983" s="21"/>
+      <c r="I983" s="20"/>
+      <c r="J983" s="20"/>
       <c r="K983" s="10" t="s">
         <v>20</v>
       </c>
@@ -45216,15 +46823,15 @@
       <c r="A984" s="6"/>
       <c r="B984" s="17"/>
       <c r="C984" s="14"/>
-      <c r="D984" s="20"/>
+      <c r="D984" s="22"/>
       <c r="E984" s="15"/>
       <c r="F984" s="15"/>
       <c r="G984" s="15"/>
       <c r="H984" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I984" s="21"/>
-      <c r="J984" s="21"/>
+      <c r="I984" s="20"/>
+      <c r="J984" s="20"/>
       <c r="K984" s="10" t="s">
         <v>20</v>
       </c>
@@ -45242,15 +46849,15 @@
       <c r="A985" s="6"/>
       <c r="B985" s="17"/>
       <c r="C985" s="14"/>
-      <c r="D985" s="20"/>
+      <c r="D985" s="22"/>
       <c r="E985" s="15"/>
       <c r="F985" s="15"/>
       <c r="G985" s="15"/>
       <c r="H985" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I985" s="21"/>
-      <c r="J985" s="21"/>
+      <c r="I985" s="20"/>
+      <c r="J985" s="20"/>
       <c r="K985" s="10" t="s">
         <v>20</v>
       </c>
@@ -45268,15 +46875,15 @@
       <c r="A986" s="6"/>
       <c r="B986" s="17"/>
       <c r="C986" s="14"/>
-      <c r="D986" s="20"/>
+      <c r="D986" s="22"/>
       <c r="E986" s="15"/>
       <c r="F986" s="15"/>
       <c r="G986" s="15"/>
       <c r="H986" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I986" s="21"/>
-      <c r="J986" s="21"/>
+      <c r="I986" s="20"/>
+      <c r="J986" s="20"/>
       <c r="K986" s="10" t="s">
         <v>20</v>
       </c>
@@ -45294,15 +46901,15 @@
       <c r="A987" s="6"/>
       <c r="B987" s="17"/>
       <c r="C987" s="14"/>
-      <c r="D987" s="20"/>
+      <c r="D987" s="22"/>
       <c r="E987" s="15"/>
       <c r="F987" s="15"/>
       <c r="G987" s="15"/>
       <c r="H987" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I987" s="21"/>
-      <c r="J987" s="21"/>
+      <c r="I987" s="20"/>
+      <c r="J987" s="20"/>
       <c r="K987" s="10" t="s">
         <v>20</v>
       </c>
@@ -45320,15 +46927,15 @@
       <c r="A988" s="6"/>
       <c r="B988" s="17"/>
       <c r="C988" s="14"/>
-      <c r="D988" s="20"/>
+      <c r="D988" s="22"/>
       <c r="E988" s="15"/>
       <c r="F988" s="15"/>
       <c r="G988" s="15"/>
       <c r="H988" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I988" s="21"/>
-      <c r="J988" s="21"/>
+      <c r="I988" s="20"/>
+      <c r="J988" s="20"/>
       <c r="K988" s="10" t="s">
         <v>20</v>
       </c>
@@ -45346,15 +46953,15 @@
       <c r="A989" s="6"/>
       <c r="B989" s="17"/>
       <c r="C989" s="14"/>
-      <c r="D989" s="20"/>
+      <c r="D989" s="22"/>
       <c r="E989" s="15"/>
       <c r="F989" s="15"/>
       <c r="G989" s="15"/>
       <c r="H989" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I989" s="21"/>
-      <c r="J989" s="21"/>
+      <c r="I989" s="20"/>
+      <c r="J989" s="20"/>
       <c r="K989" s="10" t="s">
         <v>20</v>
       </c>
@@ -45372,15 +46979,15 @@
       <c r="A990" s="6"/>
       <c r="B990" s="17"/>
       <c r="C990" s="14"/>
-      <c r="D990" s="20"/>
+      <c r="D990" s="22"/>
       <c r="E990" s="15"/>
       <c r="F990" s="15"/>
       <c r="G990" s="15"/>
       <c r="H990" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I990" s="21"/>
-      <c r="J990" s="21"/>
+      <c r="I990" s="20"/>
+      <c r="J990" s="20"/>
       <c r="K990" s="10" t="s">
         <v>20</v>
       </c>
@@ -45398,15 +47005,15 @@
       <c r="A991" s="6"/>
       <c r="B991" s="17"/>
       <c r="C991" s="14"/>
-      <c r="D991" s="20"/>
+      <c r="D991" s="22"/>
       <c r="E991" s="15"/>
       <c r="F991" s="15"/>
       <c r="G991" s="15"/>
       <c r="H991" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I991" s="21"/>
-      <c r="J991" s="21"/>
+      <c r="I991" s="20"/>
+      <c r="J991" s="20"/>
       <c r="K991" s="10" t="s">
         <v>20</v>
       </c>
@@ -45424,15 +47031,15 @@
       <c r="A992" s="6"/>
       <c r="B992" s="17"/>
       <c r="C992" s="14"/>
-      <c r="D992" s="20"/>
+      <c r="D992" s="22"/>
       <c r="E992" s="15"/>
       <c r="F992" s="15"/>
       <c r="G992" s="15"/>
       <c r="H992" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I992" s="21"/>
-      <c r="J992" s="21"/>
+      <c r="I992" s="20"/>
+      <c r="J992" s="20"/>
       <c r="K992" s="10" t="s">
         <v>20</v>
       </c>
@@ -45450,15 +47057,15 @@
       <c r="A993" s="6"/>
       <c r="B993" s="17"/>
       <c r="C993" s="14"/>
-      <c r="D993" s="20"/>
+      <c r="D993" s="22"/>
       <c r="E993" s="15"/>
       <c r="F993" s="15"/>
       <c r="G993" s="15"/>
       <c r="H993" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I993" s="21"/>
-      <c r="J993" s="21"/>
+      <c r="I993" s="20"/>
+      <c r="J993" s="20"/>
       <c r="K993" s="10" t="s">
         <v>20</v>
       </c>
@@ -45476,15 +47083,15 @@
       <c r="A994" s="6"/>
       <c r="B994" s="17"/>
       <c r="C994" s="14"/>
-      <c r="D994" s="20"/>
+      <c r="D994" s="22"/>
       <c r="E994" s="15"/>
       <c r="F994" s="15"/>
       <c r="G994" s="15"/>
       <c r="H994" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I994" s="21"/>
-      <c r="J994" s="21"/>
+      <c r="I994" s="20"/>
+      <c r="J994" s="20"/>
       <c r="K994" s="10" t="s">
         <v>20</v>
       </c>
@@ -45502,15 +47109,15 @@
       <c r="A995" s="6"/>
       <c r="B995" s="17"/>
       <c r="C995" s="14"/>
-      <c r="D995" s="20"/>
+      <c r="D995" s="22"/>
       <c r="E995" s="15"/>
       <c r="F995" s="15"/>
       <c r="G995" s="15"/>
       <c r="H995" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I995" s="21"/>
-      <c r="J995" s="21"/>
+      <c r="I995" s="20"/>
+      <c r="J995" s="20"/>
       <c r="K995" s="10" t="s">
         <v>20</v>
       </c>
@@ -45528,15 +47135,15 @@
       <c r="A996" s="6"/>
       <c r="B996" s="17"/>
       <c r="C996" s="14"/>
-      <c r="D996" s="20"/>
+      <c r="D996" s="22"/>
       <c r="E996" s="15"/>
       <c r="F996" s="15"/>
       <c r="G996" s="15"/>
       <c r="H996" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I996" s="21"/>
-      <c r="J996" s="21"/>
+      <c r="I996" s="20"/>
+      <c r="J996" s="20"/>
       <c r="K996" s="10" t="s">
         <v>20</v>
       </c>
@@ -45554,15 +47161,15 @@
       <c r="A997" s="6"/>
       <c r="B997" s="17"/>
       <c r="C997" s="14"/>
-      <c r="D997" s="20"/>
+      <c r="D997" s="22"/>
       <c r="E997" s="15"/>
       <c r="F997" s="15"/>
       <c r="G997" s="15"/>
       <c r="H997" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I997" s="21"/>
-      <c r="J997" s="21"/>
+      <c r="I997" s="20"/>
+      <c r="J997" s="20"/>
       <c r="K997" s="10" t="s">
         <v>20</v>
       </c>

--- a/data/leaves.xlsx
+++ b/data/leaves.xlsx
@@ -5,13 +5,15 @@
   <sheets>
     <sheet state="visible" name="الاجازات" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'الاجازات'!$A$1:$N$997</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8424" uniqueCount="1403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8546" uniqueCount="1515">
   <si>
     <t>leave_id</t>
   </si>
@@ -682,7 +684,7 @@
     <t>LV-79</t>
   </si>
   <si>
-    <t>راشد الشريهي</t>
+    <t>راشد فائز سويحل الشمري</t>
   </si>
   <si>
     <t>RASHID ALSHERIHI</t>
@@ -4168,18 +4170,165 @@
     <t>LV-837</t>
   </si>
   <si>
+    <t>LV-838</t>
+  </si>
+  <si>
+    <t>LV-839</t>
+  </si>
+  <si>
+    <t>LV-840</t>
+  </si>
+  <si>
     <t>فيصل سعد عبدالله الشمري</t>
   </si>
   <si>
     <t>FAISAL SAAD ALSHAMMARI</t>
   </si>
   <si>
+    <t>LV-841</t>
+  </si>
+  <si>
+    <t>LV-842</t>
+  </si>
+  <si>
+    <t>LV-843</t>
+  </si>
+  <si>
+    <t>LV-844</t>
+  </si>
+  <si>
+    <t>LV-845</t>
+  </si>
+  <si>
+    <t>LV-846</t>
+  </si>
+  <si>
+    <t>LV-847</t>
+  </si>
+  <si>
+    <t>LV-848</t>
+  </si>
+  <si>
+    <t>LV-849</t>
+  </si>
+  <si>
+    <t>LV-850</t>
+  </si>
+  <si>
+    <t>LV-851</t>
+  </si>
+  <si>
+    <t>LV-852</t>
+  </si>
+  <si>
+    <t>LV-853</t>
+  </si>
+  <si>
+    <t>LV-854</t>
+  </si>
+  <si>
+    <t>LV-855</t>
+  </si>
+  <si>
+    <t>LV-856</t>
+  </si>
+  <si>
+    <t>LV-857</t>
+  </si>
+  <si>
+    <t>LV-858</t>
+  </si>
+  <si>
+    <t>LV-859</t>
+  </si>
+  <si>
+    <t>LV-860</t>
+  </si>
+  <si>
     <t>Industrial Engineer - مهندس صناعي</t>
   </si>
   <si>
+    <t>LV-861</t>
+  </si>
+  <si>
+    <t>LV-862</t>
+  </si>
+  <si>
+    <t>LV-863</t>
+  </si>
+  <si>
+    <t>LV-864</t>
+  </si>
+  <si>
+    <t>LV-865</t>
+  </si>
+  <si>
+    <t>LV-866</t>
+  </si>
+  <si>
+    <t>LV-867</t>
+  </si>
+  <si>
+    <t>LV-868</t>
+  </si>
+  <si>
+    <t>LV-869</t>
+  </si>
+  <si>
+    <t>LV-870</t>
+  </si>
+  <si>
+    <t>LV-871</t>
+  </si>
+  <si>
+    <t>LV-872</t>
+  </si>
+  <si>
+    <t>LV-873</t>
+  </si>
+  <si>
+    <t>LV-874</t>
+  </si>
+  <si>
+    <t>LV-875</t>
+  </si>
+  <si>
+    <t>LV-876</t>
+  </si>
+  <si>
+    <t>LV-877</t>
+  </si>
+  <si>
+    <t>LV-878</t>
+  </si>
+  <si>
+    <t>LV-879</t>
+  </si>
+  <si>
     <t>NAWAF NAWAR ALOTAIBI</t>
   </si>
   <si>
+    <t>LV-880</t>
+  </si>
+  <si>
+    <t>LV-881</t>
+  </si>
+  <si>
+    <t>LV-882</t>
+  </si>
+  <si>
+    <t>LV-883</t>
+  </si>
+  <si>
+    <t>LV-884</t>
+  </si>
+  <si>
+    <t>LV-885</t>
+  </si>
+  <si>
+    <t>LV-886</t>
+  </si>
+  <si>
     <t>هتان سليمان الغازي</t>
   </si>
   <si>
@@ -4189,7 +4338,130 @@
     <t>GN | Procurement</t>
   </si>
   <si>
-    <t>راشد فائز سويحل الشمري</t>
+    <t>LV-887</t>
+  </si>
+  <si>
+    <t>LV-888</t>
+  </si>
+  <si>
+    <t>LV-889</t>
+  </si>
+  <si>
+    <t>LV-890</t>
+  </si>
+  <si>
+    <t>LV-891</t>
+  </si>
+  <si>
+    <t>LV-892</t>
+  </si>
+  <si>
+    <t>LV-893</t>
+  </si>
+  <si>
+    <t>LV-894</t>
+  </si>
+  <si>
+    <t>LV-895</t>
+  </si>
+  <si>
+    <t>LV-896</t>
+  </si>
+  <si>
+    <t>LV-897</t>
+  </si>
+  <si>
+    <t>LV-898</t>
+  </si>
+  <si>
+    <t>LV-899</t>
+  </si>
+  <si>
+    <t>LV-900</t>
+  </si>
+  <si>
+    <t>LV-901</t>
+  </si>
+  <si>
+    <t>LV-902</t>
+  </si>
+  <si>
+    <t>LV-903</t>
+  </si>
+  <si>
+    <t>LV-904</t>
+  </si>
+  <si>
+    <t>LV-905</t>
+  </si>
+  <si>
+    <t>LV-906</t>
+  </si>
+  <si>
+    <t>LV-907</t>
+  </si>
+  <si>
+    <t>LV-908</t>
+  </si>
+  <si>
+    <t>LV-909</t>
+  </si>
+  <si>
+    <t>LV-910</t>
+  </si>
+  <si>
+    <t>LV-911</t>
+  </si>
+  <si>
+    <t>LV-912</t>
+  </si>
+  <si>
+    <t>LV-913</t>
+  </si>
+  <si>
+    <t>LV-914</t>
+  </si>
+  <si>
+    <t>LV-915</t>
+  </si>
+  <si>
+    <t>LV-916</t>
+  </si>
+  <si>
+    <t>LV-917</t>
+  </si>
+  <si>
+    <t>LV-918</t>
+  </si>
+  <si>
+    <t>LV-919</t>
+  </si>
+  <si>
+    <t>LV-920</t>
+  </si>
+  <si>
+    <t>LV-921</t>
+  </si>
+  <si>
+    <t>LV-922</t>
+  </si>
+  <si>
+    <t>LV-923</t>
+  </si>
+  <si>
+    <t>LV-924</t>
+  </si>
+  <si>
+    <t>LV-925</t>
+  </si>
+  <si>
+    <t>LV-926</t>
+  </si>
+  <si>
+    <t>LV-927</t>
+  </si>
+  <si>
+    <t>LV-928</t>
   </si>
   <si>
     <t>محمد ريان خالد</t>
@@ -4198,28 +4470,94 @@
     <t>MD RAIYAN KHALID</t>
   </si>
   <si>
+    <t>LV-929</t>
+  </si>
+  <si>
     <t>هوم بهادور كومال</t>
   </si>
   <si>
     <t>HUM BAHADUR KUMAL</t>
   </si>
   <si>
+    <t>LV-930</t>
+  </si>
+  <si>
+    <t>LV-931</t>
+  </si>
+  <si>
     <t>دابلو كومار</t>
   </si>
   <si>
     <t>DABLU KUMAR</t>
   </si>
   <si>
+    <t>LV-932</t>
+  </si>
+  <si>
     <t>نانو بينوا</t>
   </si>
   <si>
     <t>NANU THANKAPPAN BINU</t>
   </si>
   <si>
+    <t>LV-933</t>
+  </si>
+  <si>
     <t>جوهر الاسلام كالو مياه</t>
   </si>
   <si>
     <t>JOHIRUL ISLAM KALU MIAH</t>
+  </si>
+  <si>
+    <t>LV-934</t>
+  </si>
+  <si>
+    <t>LV-935</t>
+  </si>
+  <si>
+    <t>LV-936</t>
+  </si>
+  <si>
+    <t>LV-937</t>
+  </si>
+  <si>
+    <t>LV-938</t>
+  </si>
+  <si>
+    <t>LV-939</t>
+  </si>
+  <si>
+    <t>LV-940</t>
+  </si>
+  <si>
+    <t>LV-941</t>
+  </si>
+  <si>
+    <t>LV-942</t>
+  </si>
+  <si>
+    <t>LV-943</t>
+  </si>
+  <si>
+    <t>LV-944</t>
+  </si>
+  <si>
+    <t>LV-945</t>
+  </si>
+  <si>
+    <t>LV-946</t>
+  </si>
+  <si>
+    <t>LV-947</t>
+  </si>
+  <si>
+    <t>LV-948</t>
+  </si>
+  <si>
+    <t>LV-949</t>
+  </si>
+  <si>
+    <t>LV-950</t>
   </si>
 </sst>
 </file>
@@ -4534,6 +4872,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N997" displayName="جدول_1" name="جدول_1" id="1">
+  <autoFilter ref="$A$1:$N$997"/>
   <tableColumns count="14">
     <tableColumn name="leave_id" id="1"/>
     <tableColumn name="employee_id" id="2"/>
@@ -40137,14 +40476,24 @@
       <c r="A805" s="6" t="s">
         <v>1350</v>
       </c>
-      <c r="B805" s="17"/>
-      <c r="C805" s="14"/>
+      <c r="B805" s="8">
+        <v>30497.0</v>
+      </c>
+      <c r="C805" s="14">
+        <v>30497.0</v>
+      </c>
       <c r="D805" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E805" s="15"/>
-      <c r="F805" s="15"/>
-      <c r="G805" s="15"/>
+      <c r="E805" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F805" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G805" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H805" s="10" t="s">
         <v>19</v>
       </c>
@@ -40171,14 +40520,24 @@
       <c r="A806" s="6" t="s">
         <v>1351</v>
       </c>
-      <c r="B806" s="17"/>
-      <c r="C806" s="14"/>
+      <c r="B806" s="8">
+        <v>30497.0</v>
+      </c>
+      <c r="C806" s="14">
+        <v>30497.0</v>
+      </c>
       <c r="D806" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E806" s="15"/>
-      <c r="F806" s="15"/>
-      <c r="G806" s="15"/>
+      <c r="E806" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F806" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G806" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H806" s="10" t="s">
         <v>19</v>
       </c>
@@ -40205,14 +40564,24 @@
       <c r="A807" s="6" t="s">
         <v>1352</v>
       </c>
-      <c r="B807" s="17"/>
-      <c r="C807" s="14"/>
+      <c r="B807" s="8">
+        <v>30497.0</v>
+      </c>
+      <c r="C807" s="14">
+        <v>30497.0</v>
+      </c>
       <c r="D807" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E807" s="15"/>
-      <c r="F807" s="15"/>
-      <c r="G807" s="15"/>
+      <c r="E807" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="F807" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="G807" s="16" t="s">
+        <v>1209</v>
+      </c>
       <c r="H807" s="10" t="s">
         <v>19</v>
       </c>
@@ -41292,7 +41661,9 @@
       <c r="R831" s="7"/>
     </row>
     <row r="832" ht="18.0" customHeight="1">
-      <c r="A832" s="6"/>
+      <c r="A832" s="6" t="s">
+        <v>1385</v>
+      </c>
       <c r="B832" s="8">
         <v>27943.0</v>
       </c>
@@ -41334,7 +41705,9 @@
       <c r="R832" s="7"/>
     </row>
     <row r="833" ht="18.0" customHeight="1">
-      <c r="A833" s="6"/>
+      <c r="A833" s="6" t="s">
+        <v>1386</v>
+      </c>
       <c r="B833" s="8">
         <v>27943.0</v>
       </c>
@@ -41376,7 +41749,9 @@
       <c r="R833" s="7"/>
     </row>
     <row r="834" ht="18.0" customHeight="1">
-      <c r="A834" s="6"/>
+      <c r="A834" s="6" t="s">
+        <v>1387</v>
+      </c>
       <c r="B834" s="8">
         <v>27509.0</v>
       </c>
@@ -41384,10 +41759,10 @@
         <v>27509.0</v>
       </c>
       <c r="D834" s="9" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="E834" s="16" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="F834" s="16" t="s">
         <v>597</v>
@@ -41418,7 +41793,9 @@
       <c r="R834" s="7"/>
     </row>
     <row r="835" ht="18.0" customHeight="1">
-      <c r="A835" s="6"/>
+      <c r="A835" s="6" t="s">
+        <v>1390</v>
+      </c>
       <c r="B835" s="8">
         <v>27509.0</v>
       </c>
@@ -41426,10 +41803,10 @@
         <v>27509.0</v>
       </c>
       <c r="D835" s="9" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="E835" s="16" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="F835" s="16" t="s">
         <v>597</v>
@@ -41460,7 +41837,9 @@
       <c r="R835" s="7"/>
     </row>
     <row r="836" ht="18.0" customHeight="1">
-      <c r="A836" s="6"/>
+      <c r="A836" s="6" t="s">
+        <v>1391</v>
+      </c>
       <c r="B836" s="8">
         <v>32083.0</v>
       </c>
@@ -41502,7 +41881,9 @@
       <c r="R836" s="7"/>
     </row>
     <row r="837" ht="18.0" customHeight="1">
-      <c r="A837" s="6"/>
+      <c r="A837" s="6" t="s">
+        <v>1392</v>
+      </c>
       <c r="B837" s="8">
         <v>30576.0</v>
       </c>
@@ -41544,7 +41925,9 @@
       <c r="R837" s="7"/>
     </row>
     <row r="838" ht="18.0" customHeight="1">
-      <c r="A838" s="6"/>
+      <c r="A838" s="6" t="s">
+        <v>1393</v>
+      </c>
       <c r="B838" s="8">
         <v>30560.0</v>
       </c>
@@ -41586,7 +41969,9 @@
       <c r="R838" s="7"/>
     </row>
     <row r="839" ht="18.0" customHeight="1">
-      <c r="A839" s="6"/>
+      <c r="A839" s="6" t="s">
+        <v>1394</v>
+      </c>
       <c r="B839" s="8">
         <v>30560.0</v>
       </c>
@@ -41628,7 +42013,9 @@
       <c r="R839" s="7"/>
     </row>
     <row r="840" ht="18.0" customHeight="1">
-      <c r="A840" s="6"/>
+      <c r="A840" s="6" t="s">
+        <v>1395</v>
+      </c>
       <c r="B840" s="8">
         <v>30560.0</v>
       </c>
@@ -41670,7 +42057,9 @@
       <c r="R840" s="7"/>
     </row>
     <row r="841" ht="18.0" customHeight="1">
-      <c r="A841" s="6"/>
+      <c r="A841" s="6" t="s">
+        <v>1396</v>
+      </c>
       <c r="B841" s="8">
         <v>30536.0</v>
       </c>
@@ -41712,7 +42101,9 @@
       <c r="R841" s="7"/>
     </row>
     <row r="842" ht="18.0" customHeight="1">
-      <c r="A842" s="6"/>
+      <c r="A842" s="6" t="s">
+        <v>1397</v>
+      </c>
       <c r="B842" s="8">
         <v>30536.0</v>
       </c>
@@ -41754,7 +42145,9 @@
       <c r="R842" s="7"/>
     </row>
     <row r="843" ht="18.0" customHeight="1">
-      <c r="A843" s="6"/>
+      <c r="A843" s="6" t="s">
+        <v>1398</v>
+      </c>
       <c r="B843" s="8">
         <v>29446.0</v>
       </c>
@@ -41796,7 +42189,9 @@
       <c r="R843" s="7"/>
     </row>
     <row r="844" ht="18.0" customHeight="1">
-      <c r="A844" s="6"/>
+      <c r="A844" s="6" t="s">
+        <v>1399</v>
+      </c>
       <c r="B844" s="8">
         <v>29446.0</v>
       </c>
@@ -41838,7 +42233,9 @@
       <c r="R844" s="7"/>
     </row>
     <row r="845" ht="18.0" customHeight="1">
-      <c r="A845" s="6"/>
+      <c r="A845" s="6" t="s">
+        <v>1400</v>
+      </c>
       <c r="B845" s="8">
         <v>29446.0</v>
       </c>
@@ -41880,7 +42277,9 @@
       <c r="R845" s="7"/>
     </row>
     <row r="846" ht="18.0" customHeight="1">
-      <c r="A846" s="6"/>
+      <c r="A846" s="6" t="s">
+        <v>1401</v>
+      </c>
       <c r="B846" s="8">
         <v>29446.0</v>
       </c>
@@ -41922,7 +42321,9 @@
       <c r="R846" s="7"/>
     </row>
     <row r="847" ht="18.0" customHeight="1">
-      <c r="A847" s="6"/>
+      <c r="A847" s="6" t="s">
+        <v>1402</v>
+      </c>
       <c r="B847" s="8">
         <v>29446.0</v>
       </c>
@@ -41964,7 +42365,9 @@
       <c r="R847" s="7"/>
     </row>
     <row r="848" ht="18.0" customHeight="1">
-      <c r="A848" s="6"/>
+      <c r="A848" s="6" t="s">
+        <v>1403</v>
+      </c>
       <c r="B848" s="8">
         <v>29446.0</v>
       </c>
@@ -42006,7 +42409,9 @@
       <c r="R848" s="7"/>
     </row>
     <row r="849" ht="18.0" customHeight="1">
-      <c r="A849" s="6"/>
+      <c r="A849" s="6" t="s">
+        <v>1404</v>
+      </c>
       <c r="B849" s="8">
         <v>29442.0</v>
       </c>
@@ -42048,7 +42453,9 @@
       <c r="R849" s="7"/>
     </row>
     <row r="850" ht="18.0" customHeight="1">
-      <c r="A850" s="6"/>
+      <c r="A850" s="6" t="s">
+        <v>1405</v>
+      </c>
       <c r="B850" s="8">
         <v>31731.0</v>
       </c>
@@ -42090,7 +42497,9 @@
       <c r="R850" s="7"/>
     </row>
     <row r="851" ht="18.0" customHeight="1">
-      <c r="A851" s="6"/>
+      <c r="A851" s="6" t="s">
+        <v>1406</v>
+      </c>
       <c r="B851" s="8">
         <v>31731.0</v>
       </c>
@@ -42132,7 +42541,9 @@
       <c r="R851" s="7"/>
     </row>
     <row r="852" ht="18.0" customHeight="1">
-      <c r="A852" s="6"/>
+      <c r="A852" s="6" t="s">
+        <v>1407</v>
+      </c>
       <c r="B852" s="8">
         <v>31731.0</v>
       </c>
@@ -42174,7 +42585,9 @@
       <c r="R852" s="7"/>
     </row>
     <row r="853" ht="18.0" customHeight="1">
-      <c r="A853" s="6"/>
+      <c r="A853" s="6" t="s">
+        <v>1408</v>
+      </c>
       <c r="B853" s="8">
         <v>31731.0</v>
       </c>
@@ -42216,7 +42629,9 @@
       <c r="R853" s="7"/>
     </row>
     <row r="854" ht="18.0" customHeight="1">
-      <c r="A854" s="6"/>
+      <c r="A854" s="6" t="s">
+        <v>1409</v>
+      </c>
       <c r="B854" s="8">
         <v>32877.0</v>
       </c>
@@ -42233,7 +42648,7 @@
         <v>58</v>
       </c>
       <c r="G854" s="18" t="s">
-        <v>1387</v>
+        <v>1410</v>
       </c>
       <c r="H854" s="10" t="s">
         <v>19</v>
@@ -42258,7 +42673,9 @@
       <c r="R854" s="7"/>
     </row>
     <row r="855" ht="18.0" customHeight="1">
-      <c r="A855" s="6"/>
+      <c r="A855" s="6" t="s">
+        <v>1411</v>
+      </c>
       <c r="B855" s="8">
         <v>31354.0</v>
       </c>
@@ -42300,7 +42717,9 @@
       <c r="R855" s="7"/>
     </row>
     <row r="856" ht="18.0" customHeight="1">
-      <c r="A856" s="6"/>
+      <c r="A856" s="6" t="s">
+        <v>1412</v>
+      </c>
       <c r="B856" s="8">
         <v>29977.0</v>
       </c>
@@ -42342,7 +42761,9 @@
       <c r="R856" s="7"/>
     </row>
     <row r="857" ht="18.0" customHeight="1">
-      <c r="A857" s="6"/>
+      <c r="A857" s="6" t="s">
+        <v>1413</v>
+      </c>
       <c r="B857" s="8">
         <v>32877.0</v>
       </c>
@@ -42359,7 +42780,7 @@
         <v>58</v>
       </c>
       <c r="G857" s="18" t="s">
-        <v>1387</v>
+        <v>1410</v>
       </c>
       <c r="H857" s="10" t="s">
         <v>19</v>
@@ -42384,7 +42805,9 @@
       <c r="R857" s="7"/>
     </row>
     <row r="858" ht="18.0" customHeight="1">
-      <c r="A858" s="6"/>
+      <c r="A858" s="6" t="s">
+        <v>1414</v>
+      </c>
       <c r="B858" s="8">
         <v>30584.0</v>
       </c>
@@ -42426,7 +42849,9 @@
       <c r="R858" s="7"/>
     </row>
     <row r="859" ht="18.0" customHeight="1">
-      <c r="A859" s="6"/>
+      <c r="A859" s="6" t="s">
+        <v>1415</v>
+      </c>
       <c r="B859" s="8">
         <v>30584.0</v>
       </c>
@@ -42468,7 +42893,9 @@
       <c r="R859" s="7"/>
     </row>
     <row r="860" ht="18.0" customHeight="1">
-      <c r="A860" s="6"/>
+      <c r="A860" s="6" t="s">
+        <v>1416</v>
+      </c>
       <c r="B860" s="8">
         <v>30584.0</v>
       </c>
@@ -42510,7 +42937,9 @@
       <c r="R860" s="7"/>
     </row>
     <row r="861" ht="18.0" customHeight="1">
-      <c r="A861" s="6"/>
+      <c r="A861" s="6" t="s">
+        <v>1417</v>
+      </c>
       <c r="B861" s="8">
         <v>29862.0</v>
       </c>
@@ -42552,7 +42981,9 @@
       <c r="R861" s="7"/>
     </row>
     <row r="862" ht="18.0" customHeight="1">
-      <c r="A862" s="6"/>
+      <c r="A862" s="6" t="s">
+        <v>1418</v>
+      </c>
       <c r="B862" s="8">
         <v>29862.0</v>
       </c>
@@ -42594,7 +43025,9 @@
       <c r="R862" s="7"/>
     </row>
     <row r="863" ht="18.0" customHeight="1">
-      <c r="A863" s="6"/>
+      <c r="A863" s="6" t="s">
+        <v>1419</v>
+      </c>
       <c r="B863" s="8">
         <v>29858.0</v>
       </c>
@@ -42636,7 +43069,9 @@
       <c r="R863" s="7"/>
     </row>
     <row r="864" ht="18.0" customHeight="1">
-      <c r="A864" s="6"/>
+      <c r="A864" s="6" t="s">
+        <v>1420</v>
+      </c>
       <c r="B864" s="8">
         <v>29858.0</v>
       </c>
@@ -42678,7 +43113,9 @@
       <c r="R864" s="7"/>
     </row>
     <row r="865" ht="18.0" customHeight="1">
-      <c r="A865" s="6"/>
+      <c r="A865" s="6" t="s">
+        <v>1421</v>
+      </c>
       <c r="B865" s="8">
         <v>29858.0</v>
       </c>
@@ -42720,7 +43157,9 @@
       <c r="R865" s="7"/>
     </row>
     <row r="866" ht="18.0" customHeight="1">
-      <c r="A866" s="6"/>
+      <c r="A866" s="6" t="s">
+        <v>1422</v>
+      </c>
       <c r="B866" s="8">
         <v>26390.0</v>
       </c>
@@ -42762,7 +43201,9 @@
       <c r="R866" s="7"/>
     </row>
     <row r="867" ht="18.0" customHeight="1">
-      <c r="A867" s="6"/>
+      <c r="A867" s="6" t="s">
+        <v>1423</v>
+      </c>
       <c r="B867" s="8">
         <v>26390.0</v>
       </c>
@@ -42804,7 +43245,9 @@
       <c r="R867" s="7"/>
     </row>
     <row r="868" ht="18.0" customHeight="1">
-      <c r="A868" s="6"/>
+      <c r="A868" s="6" t="s">
+        <v>1424</v>
+      </c>
       <c r="B868" s="8">
         <v>29628.0</v>
       </c>
@@ -42846,7 +43289,9 @@
       <c r="R868" s="7"/>
     </row>
     <row r="869" ht="18.0" customHeight="1">
-      <c r="A869" s="6"/>
+      <c r="A869" s="6" t="s">
+        <v>1425</v>
+      </c>
       <c r="B869" s="8">
         <v>29448.0</v>
       </c>
@@ -42888,7 +43333,9 @@
       <c r="R869" s="7"/>
     </row>
     <row r="870" ht="18.0" customHeight="1">
-      <c r="A870" s="6"/>
+      <c r="A870" s="6" t="s">
+        <v>1426</v>
+      </c>
       <c r="B870" s="8">
         <v>23613.0</v>
       </c>
@@ -42930,7 +43377,9 @@
       <c r="R870" s="7"/>
     </row>
     <row r="871" ht="18.0" customHeight="1">
-      <c r="A871" s="6"/>
+      <c r="A871" s="6" t="s">
+        <v>1427</v>
+      </c>
       <c r="B871" s="8">
         <v>30361.0</v>
       </c>
@@ -42972,7 +43421,9 @@
       <c r="R871" s="7"/>
     </row>
     <row r="872" ht="18.0" customHeight="1">
-      <c r="A872" s="6"/>
+      <c r="A872" s="6" t="s">
+        <v>1428</v>
+      </c>
       <c r="B872" s="8">
         <v>30361.0</v>
       </c>
@@ -43014,7 +43465,9 @@
       <c r="R872" s="7"/>
     </row>
     <row r="873" ht="18.0" customHeight="1">
-      <c r="A873" s="6"/>
+      <c r="A873" s="6" t="s">
+        <v>1429</v>
+      </c>
       <c r="B873" s="8">
         <v>27941.0</v>
       </c>
@@ -43025,7 +43478,7 @@
         <v>732</v>
       </c>
       <c r="E873" s="16" t="s">
-        <v>1388</v>
+        <v>1430</v>
       </c>
       <c r="F873" s="16" t="s">
         <v>429</v>
@@ -43056,7 +43509,9 @@
       <c r="R873" s="7"/>
     </row>
     <row r="874" ht="18.0" customHeight="1">
-      <c r="A874" s="6"/>
+      <c r="A874" s="6" t="s">
+        <v>1431</v>
+      </c>
       <c r="B874" s="8">
         <v>30361.0</v>
       </c>
@@ -43098,7 +43553,9 @@
       <c r="R874" s="7"/>
     </row>
     <row r="875" ht="18.0" customHeight="1">
-      <c r="A875" s="6"/>
+      <c r="A875" s="6" t="s">
+        <v>1432</v>
+      </c>
       <c r="B875" s="8">
         <v>31283.0</v>
       </c>
@@ -43140,7 +43597,9 @@
       <c r="R875" s="7"/>
     </row>
     <row r="876" ht="18.0" customHeight="1">
-      <c r="A876" s="6"/>
+      <c r="A876" s="6" t="s">
+        <v>1433</v>
+      </c>
       <c r="B876" s="8">
         <v>31283.0</v>
       </c>
@@ -43182,7 +43641,9 @@
       <c r="R876" s="7"/>
     </row>
     <row r="877" ht="18.0" customHeight="1">
-      <c r="A877" s="6"/>
+      <c r="A877" s="6" t="s">
+        <v>1434</v>
+      </c>
       <c r="B877" s="8">
         <v>31283.0</v>
       </c>
@@ -43224,7 +43685,9 @@
       <c r="R877" s="7"/>
     </row>
     <row r="878" ht="18.0" customHeight="1">
-      <c r="A878" s="6"/>
+      <c r="A878" s="6" t="s">
+        <v>1435</v>
+      </c>
       <c r="B878" s="8">
         <v>31283.0</v>
       </c>
@@ -43266,7 +43729,9 @@
       <c r="R878" s="7"/>
     </row>
     <row r="879" ht="18.0" customHeight="1">
-      <c r="A879" s="6"/>
+      <c r="A879" s="6" t="s">
+        <v>1436</v>
+      </c>
       <c r="B879" s="8">
         <v>31283.0</v>
       </c>
@@ -43308,7 +43773,9 @@
       <c r="R879" s="7"/>
     </row>
     <row r="880" ht="18.0" customHeight="1">
-      <c r="A880" s="6"/>
+      <c r="A880" s="6" t="s">
+        <v>1437</v>
+      </c>
       <c r="B880" s="8">
         <v>28875.0</v>
       </c>
@@ -43316,13 +43783,13 @@
         <v>28875.0</v>
       </c>
       <c r="D880" s="9" t="s">
-        <v>1389</v>
+        <v>1438</v>
       </c>
       <c r="E880" s="16" t="s">
-        <v>1390</v>
+        <v>1439</v>
       </c>
       <c r="F880" s="16" t="s">
-        <v>1391</v>
+        <v>1440</v>
       </c>
       <c r="G880" s="16" t="s">
         <v>1209</v>
@@ -43350,7 +43817,9 @@
       <c r="R880" s="7"/>
     </row>
     <row r="881" ht="18.0" customHeight="1">
-      <c r="A881" s="6"/>
+      <c r="A881" s="6" t="s">
+        <v>1441</v>
+      </c>
       <c r="B881" s="8">
         <v>28875.0</v>
       </c>
@@ -43358,13 +43827,13 @@
         <v>28875.0</v>
       </c>
       <c r="D881" s="9" t="s">
-        <v>1389</v>
+        <v>1438</v>
       </c>
       <c r="E881" s="16" t="s">
-        <v>1390</v>
+        <v>1439</v>
       </c>
       <c r="F881" s="16" t="s">
-        <v>1391</v>
+        <v>1440</v>
       </c>
       <c r="G881" s="16" t="s">
         <v>1209</v>
@@ -43392,7 +43861,9 @@
       <c r="R881" s="7"/>
     </row>
     <row r="882" ht="18.0" customHeight="1">
-      <c r="A882" s="6"/>
+      <c r="A882" s="6" t="s">
+        <v>1442</v>
+      </c>
       <c r="B882" s="8">
         <v>27164.0</v>
       </c>
@@ -43434,7 +43905,9 @@
       <c r="R882" s="7"/>
     </row>
     <row r="883" ht="18.0" customHeight="1">
-      <c r="A883" s="6"/>
+      <c r="A883" s="6" t="s">
+        <v>1443</v>
+      </c>
       <c r="B883" s="8">
         <v>32391.0</v>
       </c>
@@ -43476,7 +43949,9 @@
       <c r="R883" s="7"/>
     </row>
     <row r="884" ht="18.0" customHeight="1">
-      <c r="A884" s="6"/>
+      <c r="A884" s="6" t="s">
+        <v>1444</v>
+      </c>
       <c r="B884" s="8">
         <v>31304.0</v>
       </c>
@@ -43518,7 +43993,9 @@
       <c r="R884" s="7"/>
     </row>
     <row r="885" ht="18.0" customHeight="1">
-      <c r="A885" s="6"/>
+      <c r="A885" s="6" t="s">
+        <v>1445</v>
+      </c>
       <c r="B885" s="8">
         <v>30646.0</v>
       </c>
@@ -43560,7 +44037,9 @@
       <c r="R885" s="7"/>
     </row>
     <row r="886" ht="18.0" customHeight="1">
-      <c r="A886" s="6"/>
+      <c r="A886" s="6" t="s">
+        <v>1446</v>
+      </c>
       <c r="B886" s="8">
         <v>31720.0</v>
       </c>
@@ -43602,7 +44081,9 @@
       <c r="R886" s="7"/>
     </row>
     <row r="887" ht="18.0" customHeight="1">
-      <c r="A887" s="6"/>
+      <c r="A887" s="6" t="s">
+        <v>1447</v>
+      </c>
       <c r="B887" s="8">
         <v>31720.0</v>
       </c>
@@ -43644,7 +44125,9 @@
       <c r="R887" s="7"/>
     </row>
     <row r="888" ht="18.0" customHeight="1">
-      <c r="A888" s="6"/>
+      <c r="A888" s="6" t="s">
+        <v>1448</v>
+      </c>
       <c r="B888" s="8">
         <v>31720.0</v>
       </c>
@@ -43686,7 +44169,9 @@
       <c r="R888" s="7"/>
     </row>
     <row r="889" ht="18.0" customHeight="1">
-      <c r="A889" s="6"/>
+      <c r="A889" s="6" t="s">
+        <v>1449</v>
+      </c>
       <c r="B889" s="8">
         <v>31720.0</v>
       </c>
@@ -43728,7 +44213,9 @@
       <c r="R889" s="7"/>
     </row>
     <row r="890" ht="18.0" customHeight="1">
-      <c r="A890" s="6"/>
+      <c r="A890" s="6" t="s">
+        <v>1450</v>
+      </c>
       <c r="B890" s="8">
         <v>31720.0</v>
       </c>
@@ -43770,7 +44257,9 @@
       <c r="R890" s="7"/>
     </row>
     <row r="891" ht="18.0" customHeight="1">
-      <c r="A891" s="6"/>
+      <c r="A891" s="6" t="s">
+        <v>1451</v>
+      </c>
       <c r="B891" s="8">
         <v>30858.0</v>
       </c>
@@ -43812,7 +44301,9 @@
       <c r="R891" s="7"/>
     </row>
     <row r="892" ht="18.0" customHeight="1">
-      <c r="A892" s="6"/>
+      <c r="A892" s="6" t="s">
+        <v>1452</v>
+      </c>
       <c r="B892" s="8">
         <v>30858.0</v>
       </c>
@@ -43854,7 +44345,9 @@
       <c r="R892" s="7"/>
     </row>
     <row r="893" ht="18.0" customHeight="1">
-      <c r="A893" s="6"/>
+      <c r="A893" s="6" t="s">
+        <v>1453</v>
+      </c>
       <c r="B893" s="8">
         <v>30858.0</v>
       </c>
@@ -43896,7 +44389,9 @@
       <c r="R893" s="7"/>
     </row>
     <row r="894" ht="18.0" customHeight="1">
-      <c r="A894" s="6"/>
+      <c r="A894" s="6" t="s">
+        <v>1454</v>
+      </c>
       <c r="B894" s="8">
         <v>30574.0</v>
       </c>
@@ -43938,7 +44433,9 @@
       <c r="R894" s="7"/>
     </row>
     <row r="895" ht="18.0" customHeight="1">
-      <c r="A895" s="6"/>
+      <c r="A895" s="6" t="s">
+        <v>1455</v>
+      </c>
       <c r="B895" s="8">
         <v>30574.0</v>
       </c>
@@ -43980,7 +44477,9 @@
       <c r="R895" s="7"/>
     </row>
     <row r="896" ht="18.0" customHeight="1">
-      <c r="A896" s="6"/>
+      <c r="A896" s="6" t="s">
+        <v>1456</v>
+      </c>
       <c r="B896" s="8">
         <v>30574.0</v>
       </c>
@@ -44022,7 +44521,9 @@
       <c r="R896" s="7"/>
     </row>
     <row r="897" ht="18.0" customHeight="1">
-      <c r="A897" s="6"/>
+      <c r="A897" s="6" t="s">
+        <v>1457</v>
+      </c>
       <c r="B897" s="8">
         <v>28211.0</v>
       </c>
@@ -44064,7 +44565,9 @@
       <c r="R897" s="7"/>
     </row>
     <row r="898" ht="18.0" customHeight="1">
-      <c r="A898" s="6"/>
+      <c r="A898" s="6" t="s">
+        <v>1458</v>
+      </c>
       <c r="B898" s="8">
         <v>28211.0</v>
       </c>
@@ -44106,7 +44609,9 @@
       <c r="R898" s="7"/>
     </row>
     <row r="899" ht="18.0" customHeight="1">
-      <c r="A899" s="6"/>
+      <c r="A899" s="6" t="s">
+        <v>1459</v>
+      </c>
       <c r="B899" s="8">
         <v>28211.0</v>
       </c>
@@ -44148,7 +44653,9 @@
       <c r="R899" s="7"/>
     </row>
     <row r="900" ht="18.0" customHeight="1">
-      <c r="A900" s="6"/>
+      <c r="A900" s="6" t="s">
+        <v>1460</v>
+      </c>
       <c r="B900" s="8">
         <v>28211.0</v>
       </c>
@@ -44190,7 +44697,9 @@
       <c r="R900" s="7"/>
     </row>
     <row r="901" ht="18.0" customHeight="1">
-      <c r="A901" s="6"/>
+      <c r="A901" s="6" t="s">
+        <v>1461</v>
+      </c>
       <c r="B901" s="8">
         <v>29756.0</v>
       </c>
@@ -44232,7 +44741,9 @@
       <c r="R901" s="7"/>
     </row>
     <row r="902" ht="18.0" customHeight="1">
-      <c r="A902" s="6"/>
+      <c r="A902" s="6" t="s">
+        <v>1462</v>
+      </c>
       <c r="B902" s="8">
         <v>27864.0</v>
       </c>
@@ -44274,7 +44785,9 @@
       <c r="R902" s="7"/>
     </row>
     <row r="903" ht="18.0" customHeight="1">
-      <c r="A903" s="6"/>
+      <c r="A903" s="6" t="s">
+        <v>1463</v>
+      </c>
       <c r="B903" s="8">
         <v>28215.0</v>
       </c>
@@ -44316,7 +44829,9 @@
       <c r="R903" s="7"/>
     </row>
     <row r="904" ht="18.0" customHeight="1">
-      <c r="A904" s="6"/>
+      <c r="A904" s="6" t="s">
+        <v>1464</v>
+      </c>
       <c r="B904" s="8">
         <v>31279.0</v>
       </c>
@@ -44358,7 +44873,9 @@
       <c r="R904" s="7"/>
     </row>
     <row r="905" ht="18.0" customHeight="1">
-      <c r="A905" s="6"/>
+      <c r="A905" s="6" t="s">
+        <v>1465</v>
+      </c>
       <c r="B905" s="8">
         <v>31279.0</v>
       </c>
@@ -44400,7 +44917,9 @@
       <c r="R905" s="7"/>
     </row>
     <row r="906" ht="18.0" customHeight="1">
-      <c r="A906" s="6"/>
+      <c r="A906" s="6" t="s">
+        <v>1466</v>
+      </c>
       <c r="B906" s="8">
         <v>31279.0</v>
       </c>
@@ -44442,7 +44961,9 @@
       <c r="R906" s="7"/>
     </row>
     <row r="907" ht="18.0" customHeight="1">
-      <c r="A907" s="6"/>
+      <c r="A907" s="6" t="s">
+        <v>1467</v>
+      </c>
       <c r="B907" s="8">
         <v>31279.0</v>
       </c>
@@ -44484,7 +45005,9 @@
       <c r="R907" s="7"/>
     </row>
     <row r="908" ht="18.0" customHeight="1">
-      <c r="A908" s="6"/>
+      <c r="A908" s="6" t="s">
+        <v>1468</v>
+      </c>
       <c r="B908" s="8">
         <v>31279.0</v>
       </c>
@@ -44526,7 +45049,9 @@
       <c r="R908" s="7"/>
     </row>
     <row r="909" ht="18.0" customHeight="1">
-      <c r="A909" s="6"/>
+      <c r="A909" s="6" t="s">
+        <v>1469</v>
+      </c>
       <c r="B909" s="8">
         <v>31271.0</v>
       </c>
@@ -44564,7 +45089,9 @@
       <c r="R909" s="7"/>
     </row>
     <row r="910" ht="18.0" customHeight="1">
-      <c r="A910" s="6"/>
+      <c r="A910" s="6" t="s">
+        <v>1470</v>
+      </c>
       <c r="B910" s="8">
         <v>31271.0</v>
       </c>
@@ -44602,7 +45129,9 @@
       <c r="R910" s="7"/>
     </row>
     <row r="911" ht="18.0" customHeight="1">
-      <c r="A911" s="6"/>
+      <c r="A911" s="6" t="s">
+        <v>1471</v>
+      </c>
       <c r="B911" s="8">
         <v>30353.0</v>
       </c>
@@ -44644,7 +45173,9 @@
       <c r="R911" s="7"/>
     </row>
     <row r="912" ht="18.0" customHeight="1">
-      <c r="A912" s="6"/>
+      <c r="A912" s="6" t="s">
+        <v>1472</v>
+      </c>
       <c r="B912" s="8">
         <v>32348.0</v>
       </c>
@@ -44686,7 +45217,9 @@
       <c r="R912" s="7"/>
     </row>
     <row r="913" ht="18.0" customHeight="1">
-      <c r="A913" s="6"/>
+      <c r="A913" s="6" t="s">
+        <v>1473</v>
+      </c>
       <c r="B913" s="8">
         <v>32348.0</v>
       </c>
@@ -44728,7 +45261,9 @@
       <c r="R913" s="7"/>
     </row>
     <row r="914" ht="18.0" customHeight="1">
-      <c r="A914" s="6"/>
+      <c r="A914" s="6" t="s">
+        <v>1474</v>
+      </c>
       <c r="B914" s="8">
         <v>31962.0</v>
       </c>
@@ -44770,7 +45305,9 @@
       <c r="R914" s="7"/>
     </row>
     <row r="915" ht="18.0" customHeight="1">
-      <c r="A915" s="6"/>
+      <c r="A915" s="6" t="s">
+        <v>1475</v>
+      </c>
       <c r="B915" s="8">
         <v>31962.0</v>
       </c>
@@ -44812,7 +45349,9 @@
       <c r="R915" s="7"/>
     </row>
     <row r="916" ht="18.0" customHeight="1">
-      <c r="A916" s="6"/>
+      <c r="A916" s="6" t="s">
+        <v>1476</v>
+      </c>
       <c r="B916" s="8">
         <v>31962.0</v>
       </c>
@@ -44854,7 +45393,9 @@
       <c r="R916" s="7"/>
     </row>
     <row r="917" ht="18.0" customHeight="1">
-      <c r="A917" s="6"/>
+      <c r="A917" s="6" t="s">
+        <v>1477</v>
+      </c>
       <c r="B917" s="8">
         <v>30497.0</v>
       </c>
@@ -44862,7 +45403,7 @@
         <v>30497.0</v>
       </c>
       <c r="D917" s="9" t="s">
-        <v>1392</v>
+        <v>223</v>
       </c>
       <c r="E917" s="16" t="s">
         <v>224</v>
@@ -44896,7 +45437,9 @@
       <c r="R917" s="7"/>
     </row>
     <row r="918" ht="18.0" customHeight="1">
-      <c r="A918" s="6"/>
+      <c r="A918" s="6" t="s">
+        <v>1478</v>
+      </c>
       <c r="B918" s="8">
         <v>30497.0</v>
       </c>
@@ -44904,7 +45447,7 @@
         <v>30497.0</v>
       </c>
       <c r="D918" s="9" t="s">
-        <v>1392</v>
+        <v>223</v>
       </c>
       <c r="E918" s="16" t="s">
         <v>224</v>
@@ -44938,7 +45481,9 @@
       <c r="R918" s="7"/>
     </row>
     <row r="919" ht="18.0" customHeight="1">
-      <c r="A919" s="6"/>
+      <c r="A919" s="6" t="s">
+        <v>1479</v>
+      </c>
       <c r="B919" s="8">
         <v>30497.0</v>
       </c>
@@ -44946,7 +45491,7 @@
         <v>30497.0</v>
       </c>
       <c r="D919" s="9" t="s">
-        <v>1392</v>
+        <v>223</v>
       </c>
       <c r="E919" s="16" t="s">
         <v>224</v>
@@ -44980,7 +45525,9 @@
       <c r="R919" s="7"/>
     </row>
     <row r="920" ht="18.0" customHeight="1">
-      <c r="A920" s="6"/>
+      <c r="A920" s="6" t="s">
+        <v>1480</v>
+      </c>
       <c r="B920" s="8">
         <v>30497.0</v>
       </c>
@@ -44988,7 +45535,7 @@
         <v>30497.0</v>
       </c>
       <c r="D920" s="9" t="s">
-        <v>1392</v>
+        <v>223</v>
       </c>
       <c r="E920" s="16" t="s">
         <v>224</v>
@@ -45022,7 +45569,9 @@
       <c r="R920" s="7"/>
     </row>
     <row r="921" ht="18.0" customHeight="1">
-      <c r="A921" s="6"/>
+      <c r="A921" s="6" t="s">
+        <v>1481</v>
+      </c>
       <c r="B921" s="8">
         <v>26796.0</v>
       </c>
@@ -45064,7 +45613,9 @@
       <c r="R921" s="7"/>
     </row>
     <row r="922" ht="18.0" customHeight="1">
-      <c r="A922" s="6"/>
+      <c r="A922" s="6" t="s">
+        <v>1482</v>
+      </c>
       <c r="B922" s="8">
         <v>31456.0</v>
       </c>
@@ -45072,10 +45623,10 @@
         <v>31456.0</v>
       </c>
       <c r="D922" s="9" t="s">
-        <v>1393</v>
+        <v>1483</v>
       </c>
       <c r="E922" s="16" t="s">
-        <v>1394</v>
+        <v>1484</v>
       </c>
       <c r="F922" s="16" t="s">
         <v>429</v>
@@ -45106,7 +45657,9 @@
       <c r="R922" s="7"/>
     </row>
     <row r="923" ht="18.0" customHeight="1">
-      <c r="A923" s="6"/>
+      <c r="A923" s="6" t="s">
+        <v>1485</v>
+      </c>
       <c r="B923" s="8">
         <v>27912.0</v>
       </c>
@@ -45114,10 +45667,10 @@
         <v>27912.0</v>
       </c>
       <c r="D923" s="9" t="s">
-        <v>1395</v>
+        <v>1486</v>
       </c>
       <c r="E923" s="16" t="s">
-        <v>1396</v>
+        <v>1487</v>
       </c>
       <c r="F923" s="16" t="s">
         <v>209</v>
@@ -45148,7 +45701,9 @@
       <c r="R923" s="7"/>
     </row>
     <row r="924" ht="18.0" customHeight="1">
-      <c r="A924" s="6"/>
+      <c r="A924" s="6" t="s">
+        <v>1488</v>
+      </c>
       <c r="B924" s="8">
         <v>27912.0</v>
       </c>
@@ -45156,10 +45711,10 @@
         <v>27912.0</v>
       </c>
       <c r="D924" s="9" t="s">
-        <v>1395</v>
+        <v>1486</v>
       </c>
       <c r="E924" s="16" t="s">
-        <v>1396</v>
+        <v>1487</v>
       </c>
       <c r="F924" s="16" t="s">
         <v>209</v>
@@ -45190,7 +45745,9 @@
       <c r="R924" s="7"/>
     </row>
     <row r="925" ht="18.0" customHeight="1">
-      <c r="A925" s="6"/>
+      <c r="A925" s="6" t="s">
+        <v>1489</v>
+      </c>
       <c r="B925" s="8">
         <v>32031.0</v>
       </c>
@@ -45198,10 +45755,10 @@
         <v>32031.0</v>
       </c>
       <c r="D925" s="9" t="s">
-        <v>1397</v>
+        <v>1490</v>
       </c>
       <c r="E925" s="16" t="s">
-        <v>1398</v>
+        <v>1491</v>
       </c>
       <c r="F925" s="16" t="s">
         <v>326</v>
@@ -45232,7 +45789,9 @@
       <c r="R925" s="7"/>
     </row>
     <row r="926" ht="18.0" customHeight="1">
-      <c r="A926" s="6"/>
+      <c r="A926" s="6" t="s">
+        <v>1492</v>
+      </c>
       <c r="B926" s="8">
         <v>17666.0</v>
       </c>
@@ -45240,10 +45799,10 @@
         <v>17666.0</v>
       </c>
       <c r="D926" s="9" t="s">
-        <v>1399</v>
+        <v>1493</v>
       </c>
       <c r="E926" s="16" t="s">
-        <v>1400</v>
+        <v>1494</v>
       </c>
       <c r="F926" s="16" t="s">
         <v>326</v>
@@ -45274,7 +45833,9 @@
       <c r="R926" s="7"/>
     </row>
     <row r="927" ht="18.0" customHeight="1">
-      <c r="A927" s="6"/>
+      <c r="A927" s="6" t="s">
+        <v>1495</v>
+      </c>
       <c r="B927" s="8">
         <v>26226.0</v>
       </c>
@@ -45282,10 +45843,10 @@
         <v>26226.0</v>
       </c>
       <c r="D927" s="9" t="s">
-        <v>1401</v>
+        <v>1496</v>
       </c>
       <c r="E927" s="16" t="s">
-        <v>1402</v>
+        <v>1497</v>
       </c>
       <c r="F927" s="16" t="s">
         <v>326</v>
@@ -45316,7 +45877,9 @@
       <c r="R927" s="7"/>
     </row>
     <row r="928" ht="18.0" customHeight="1">
-      <c r="A928" s="6"/>
+      <c r="A928" s="6" t="s">
+        <v>1498</v>
+      </c>
       <c r="B928" s="8">
         <v>31442.0</v>
       </c>
@@ -45354,7 +45917,9 @@
       <c r="R928" s="7"/>
     </row>
     <row r="929" ht="18.0" customHeight="1">
-      <c r="A929" s="6"/>
+      <c r="A929" s="6" t="s">
+        <v>1499</v>
+      </c>
       <c r="B929" s="8">
         <v>31442.0</v>
       </c>
@@ -45392,7 +45957,9 @@
       <c r="R929" s="7"/>
     </row>
     <row r="930" ht="18.0" customHeight="1">
-      <c r="A930" s="6"/>
+      <c r="A930" s="6" t="s">
+        <v>1500</v>
+      </c>
       <c r="B930" s="8">
         <v>31442.0</v>
       </c>
@@ -45430,7 +45997,9 @@
       <c r="R930" s="7"/>
     </row>
     <row r="931" ht="18.0" customHeight="1">
-      <c r="A931" s="6"/>
+      <c r="A931" s="6" t="s">
+        <v>1501</v>
+      </c>
       <c r="B931" s="8">
         <v>31442.0</v>
       </c>
@@ -45468,7 +46037,9 @@
       <c r="R931" s="7"/>
     </row>
     <row r="932" ht="18.0" customHeight="1">
-      <c r="A932" s="6"/>
+      <c r="A932" s="6" t="s">
+        <v>1502</v>
+      </c>
       <c r="B932" s="17"/>
       <c r="C932" s="14"/>
       <c r="D932" s="22"/>
@@ -45494,7 +46065,9 @@
       <c r="R932" s="7"/>
     </row>
     <row r="933" ht="18.0" customHeight="1">
-      <c r="A933" s="6"/>
+      <c r="A933" s="6" t="s">
+        <v>1503</v>
+      </c>
       <c r="B933" s="17"/>
       <c r="C933" s="14"/>
       <c r="D933" s="22"/>
@@ -45520,7 +46093,9 @@
       <c r="R933" s="7"/>
     </row>
     <row r="934" ht="18.0" customHeight="1">
-      <c r="A934" s="6"/>
+      <c r="A934" s="6" t="s">
+        <v>1504</v>
+      </c>
       <c r="B934" s="17"/>
       <c r="C934" s="14"/>
       <c r="D934" s="22"/>
@@ -45546,7 +46121,9 @@
       <c r="R934" s="7"/>
     </row>
     <row r="935" ht="18.0" customHeight="1">
-      <c r="A935" s="6"/>
+      <c r="A935" s="6" t="s">
+        <v>1505</v>
+      </c>
       <c r="B935" s="17"/>
       <c r="C935" s="14"/>
       <c r="D935" s="22"/>
@@ -45572,7 +46149,9 @@
       <c r="R935" s="7"/>
     </row>
     <row r="936" ht="18.0" customHeight="1">
-      <c r="A936" s="6"/>
+      <c r="A936" s="6" t="s">
+        <v>1506</v>
+      </c>
       <c r="B936" s="17"/>
       <c r="C936" s="14"/>
       <c r="D936" s="22"/>
@@ -45598,7 +46177,9 @@
       <c r="R936" s="7"/>
     </row>
     <row r="937" ht="18.0" customHeight="1">
-      <c r="A937" s="6"/>
+      <c r="A937" s="6" t="s">
+        <v>1507</v>
+      </c>
       <c r="B937" s="17"/>
       <c r="C937" s="14"/>
       <c r="D937" s="22"/>
@@ -45624,7 +46205,9 @@
       <c r="R937" s="7"/>
     </row>
     <row r="938" ht="18.0" customHeight="1">
-      <c r="A938" s="6"/>
+      <c r="A938" s="6" t="s">
+        <v>1508</v>
+      </c>
       <c r="B938" s="17"/>
       <c r="C938" s="14"/>
       <c r="D938" s="22"/>
@@ -45650,7 +46233,9 @@
       <c r="R938" s="7"/>
     </row>
     <row r="939" ht="18.0" customHeight="1">
-      <c r="A939" s="6"/>
+      <c r="A939" s="6" t="s">
+        <v>1509</v>
+      </c>
       <c r="B939" s="17"/>
       <c r="C939" s="14"/>
       <c r="D939" s="22"/>
@@ -45676,7 +46261,9 @@
       <c r="R939" s="7"/>
     </row>
     <row r="940" ht="18.0" customHeight="1">
-      <c r="A940" s="6"/>
+      <c r="A940" s="6" t="s">
+        <v>1510</v>
+      </c>
       <c r="B940" s="17"/>
       <c r="C940" s="14"/>
       <c r="D940" s="22"/>
@@ -45702,7 +46289,9 @@
       <c r="R940" s="7"/>
     </row>
     <row r="941" ht="18.0" customHeight="1">
-      <c r="A941" s="6"/>
+      <c r="A941" s="6" t="s">
+        <v>1511</v>
+      </c>
       <c r="B941" s="17"/>
       <c r="C941" s="14"/>
       <c r="D941" s="22"/>
@@ -45728,7 +46317,9 @@
       <c r="R941" s="7"/>
     </row>
     <row r="942" ht="18.0" customHeight="1">
-      <c r="A942" s="6"/>
+      <c r="A942" s="6" t="s">
+        <v>1512</v>
+      </c>
       <c r="B942" s="17"/>
       <c r="C942" s="14"/>
       <c r="D942" s="22"/>
@@ -45754,7 +46345,9 @@
       <c r="R942" s="7"/>
     </row>
     <row r="943" ht="18.0" customHeight="1">
-      <c r="A943" s="6"/>
+      <c r="A943" s="6" t="s">
+        <v>1513</v>
+      </c>
       <c r="B943" s="17"/>
       <c r="C943" s="14"/>
       <c r="D943" s="22"/>
@@ -45780,7 +46373,9 @@
       <c r="R943" s="7"/>
     </row>
     <row r="944" ht="18.0" customHeight="1">
-      <c r="A944" s="6"/>
+      <c r="A944" s="6" t="s">
+        <v>1514</v>
+      </c>
       <c r="B944" s="17"/>
       <c r="C944" s="14"/>
       <c r="D944" s="22"/>
